--- a/data/Data_v11.xlsx
+++ b/data/Data_v11.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/younglee/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/younglee/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2149BDE1-3752-A841-8A90-37F48CBC3072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD185A2-2DF1-6A4A-A9EF-290895718D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="760" windowWidth="16760" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12640" yWindow="760" windowWidth="16760" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -3017,103 +3017,103 @@
       </c>
       <c r="C3" s="3">
         <f>VLOOKUP(C1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>2372360.2275402769</v>
+        <v>2264619.850394343</v>
       </c>
       <c r="D3" s="3">
         <f>VLOOKUP(D1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>3778827.5511404499</v>
+        <v>3478501.5186917325</v>
       </c>
       <c r="E3" s="3">
         <f>VLOOKUP(E1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>3778827.5511404499</v>
+        <v>3366291.7922823224</v>
       </c>
       <c r="F3" s="3">
         <f>VLOOKUP(F1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>4340601.6674776226</v>
+        <v>3764382.0574718602</v>
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP(G1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>13285622.459349569</v>
+        <v>11243465.644637324</v>
       </c>
       <c r="H3" s="3">
         <f>VLOOKUP(H1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>13285622.459349569</v>
+        <v>10988196.042798292</v>
       </c>
       <c r="I3" s="3">
         <f>VLOOKUP(I1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>13824692.508017804</v>
+        <v>11192567.646229263</v>
       </c>
       <c r="J3" s="3">
         <f>VLOOKUP(J1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>20267333.697750408</v>
+        <v>16107662.589478489</v>
       </c>
       <c r="K3" s="3">
         <f>VLOOKUP(K1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>20267333.697750408</v>
+        <v>15806750.211433291</v>
       </c>
       <c r="L3" s="3">
         <f>VLOOKUP(L1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>27586831.052333623</v>
+        <v>21153919.357160635</v>
       </c>
       <c r="M3" s="3">
         <f>VLOOKUP(M1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>32941156.593877025</v>
+        <v>24828138.113987666</v>
       </c>
       <c r="N3" s="3">
         <f>VLOOKUP(N1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>37620551.679753549</v>
+        <v>27635499.279251926</v>
       </c>
       <c r="O3" s="3">
         <f>VLOOKUP(O1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>37620551.679753549</v>
+        <v>26934205.0131284</v>
       </c>
       <c r="P3" s="3">
         <f>VLOOKUP(P1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>37620551.679753549</v>
+        <v>26250707.192175917</v>
       </c>
       <c r="Q3" s="3">
         <f>VLOOKUP(Q1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>41729207.752535008</v>
+        <v>28378722.00031393</v>
       </c>
       <c r="R3" s="3">
         <f>VLOOKUP(R1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>41729207.752535008</v>
+        <v>27658567.288519904</v>
       </c>
       <c r="S3" s="3">
         <f>VLOOKUP(S1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>46264513.511275306</v>
+        <v>29886453.793272253</v>
       </c>
       <c r="T3" s="3">
         <f>VLOOKUP(T1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>46264513.511275306</v>
+        <v>29128038.015500385</v>
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>50577489.410324246</v>
+        <v>31035399.99356623</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>50577489.410324246</v>
+        <v>30247827.898616642</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54250296.375863224</v>
+        <v>31621020.878267676</v>
       </c>
       <c r="X3" s="3">
         <f>VLOOKUP(X1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54250296.375863224</v>
+        <v>30818587.732160185</v>
       </c>
       <c r="Y3" s="3">
         <f>VLOOKUP(Y1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54250296.375863224</v>
+        <v>30036517.589399442</v>
       </c>
       <c r="Z3" s="3">
         <f>VLOOKUP(Z1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54250296.375863224</v>
+        <v>29274293.706743591</v>
       </c>
       <c r="AA3" s="3">
         <f>VLOOKUP(AA1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54250296.375863224</v>
+        <v>28531412.454123393</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3141,87 +3141,87 @@
       </c>
       <c r="G4" s="3">
         <f>(VLOOKUP(G1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(G1,h2portion!$C$1:$AB$5,3)/HLOOKUP(G1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1593581.9027192548</v>
+        <v>1348629.5753143742</v>
       </c>
       <c r="H4" s="3">
         <f>(VLOOKUP(H1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(H1,h2portion!$C$1:$AB$5,3)/HLOOKUP(H1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1298726.7363034924</v>
+        <v>1074143.4229514475</v>
       </c>
       <c r="I4" s="3">
         <f>(VLOOKUP(I1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(I1,h2portion!$C$1:$AB$5,3)/HLOOKUP(I1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1817988.8248739468</v>
+        <v>1471856.4547232741</v>
       </c>
       <c r="J4" s="3">
         <f>(VLOOKUP(J1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,3)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3053238.8832500828</v>
+        <v>2426591.6015349999</v>
       </c>
       <c r="K4" s="3">
         <f>(VLOOKUP(K1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,3)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3053238.8832500828</v>
+        <v>2381259.6705173133</v>
       </c>
       <c r="L4" s="3">
         <f>(VLOOKUP(L1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,3)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4616918.0605922155</v>
+        <v>3540309.2202619775</v>
       </c>
       <c r="M4" s="3">
         <f>(VLOOKUP(M1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,3)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5643286.2916632388</v>
+        <v>4253411.4145898465</v>
       </c>
       <c r="N4" s="3">
         <f>(VLOOKUP(N1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,3)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>6540543.3473375458</v>
+        <v>4804586.1341937333</v>
       </c>
       <c r="O4" s="3">
         <f>(VLOOKUP(O1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,3)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>6540543.3473375458</v>
+        <v>4682662.203203409</v>
       </c>
       <c r="P4" s="3">
         <f>(VLOOKUP(P1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,3)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>6540543.3473375458</v>
+        <v>4563832.2837539194</v>
       </c>
       <c r="Q4" s="3">
         <f>(VLOOKUP(Q1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>7328251.4888862483</v>
+        <v>4983713.397694584</v>
       </c>
       <c r="R4" s="3">
         <f>(VLOOKUP(R1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,3)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>6767964.2363150828</v>
+        <v>4485879.4191951826</v>
       </c>
       <c r="S4" s="3">
         <f>(VLOOKUP(S1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,3)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>7570926.0310452878</v>
+        <v>4890749.16877646</v>
       </c>
       <c r="T4" s="3">
         <f>(VLOOKUP(T1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,3)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>7570926.0310452878</v>
+        <v>4766638.715245178</v>
       </c>
       <c r="U4" s="3">
         <f>(VLOOKUP(U1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,3)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8334542.7829103386</v>
+        <v>5114248.8891176973</v>
       </c>
       <c r="V4" s="3">
         <f>(VLOOKUP(V1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,3)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8334542.7829103386</v>
+        <v>4984466.7786074094</v>
       </c>
       <c r="W4" s="3">
         <f>(VLOOKUP(W1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,3)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8984741.0302993003</v>
+        <v>5236960.9510801807</v>
       </c>
       <c r="X4" s="3">
         <f>(VLOOKUP(X1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,3)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8984741.0302993003</v>
+        <v>5104064.8289658725</v>
       </c>
       <c r="Y4" s="3">
         <f>(VLOOKUP(Y1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8984741.0302993003</v>
+        <v>4974541.1550019328</v>
       </c>
       <c r="Z4" s="3">
         <f>(VLOOKUP(Z1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8984741.0302993003</v>
+        <v>4848304.3480115291</v>
       </c>
       <c r="AA4" s="3">
         <f>(VLOOKUP(AA1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,3)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8984741.0302993022</v>
+        <v>4725270.9985748157</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3249,87 +3249,87 @@
       </c>
       <c r="G5" s="3">
         <f>(VLOOKUP(G1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(G1,h2portion!$C$1:$AB$5,4)/HLOOKUP(G1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1716165.1260053513</v>
+        <v>1452370.3118770183</v>
       </c>
       <c r="H5" s="3">
         <f>(VLOOKUP(H1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(H1,h2portion!$C$1:$AB$5,4)/HLOOKUP(H1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1646060.630896287</v>
+        <v>1361414.3383919511</v>
       </c>
       <c r="I5" s="3">
         <f>(VLOOKUP(I1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(I1,h2portion!$C$1:$AB$5,4)/HLOOKUP(I1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2304195.1385030258</v>
+        <v>1865492.4833120569</v>
       </c>
       <c r="J5" s="3">
         <f>(VLOOKUP(J1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,4)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3869802.7706309189</v>
+        <v>3075563.7740385467</v>
       </c>
       <c r="K5" s="3">
         <f>(VLOOKUP(K1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,4)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3869802.7706309189</v>
+        <v>3018108.1870510136</v>
       </c>
       <c r="L5" s="3">
         <f>(VLOOKUP(L1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,4)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5851675.216331996</v>
+        <v>4487136.1047506472</v>
       </c>
       <c r="M5" s="3">
         <f>(VLOOKUP(M1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,4)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>7152537.2766429428</v>
+        <v>5390951.6766313175</v>
       </c>
       <c r="N5" s="3">
         <f>(VLOOKUP(N1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,4)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8289758.4286022391</v>
+        <v>6089533.5886874069</v>
       </c>
       <c r="O5" s="3">
         <f>(VLOOKUP(O1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,4)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8289758.4286022391</v>
+        <v>5935002.0947578093</v>
       </c>
       <c r="P5" s="3">
         <f>(VLOOKUP(P1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,4)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8289758.4286022391</v>
+        <v>5784392.0805718284</v>
       </c>
       <c r="Q5" s="3">
         <f>(VLOOKUP(Q1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>9288132.7010302451</v>
+        <v>6316566.9807989514</v>
       </c>
       <c r="R5" s="3">
         <f>(VLOOKUP(R1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,4)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>7701476.5447723372</v>
+        <v>5104621.4080496915</v>
       </c>
       <c r="S5" s="3">
         <f>(VLOOKUP(S1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,4)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8615191.6904998105</v>
+        <v>5565335.2610214902</v>
       </c>
       <c r="T5" s="3">
         <f>(VLOOKUP(T1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,4)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>8615191.6904998105</v>
+        <v>5424106.1242445139</v>
       </c>
       <c r="U5" s="3">
         <f>(VLOOKUP(U1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,4)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>9484134.8908979744</v>
+        <v>5819662.528996001</v>
       </c>
       <c r="V5" s="3">
         <f>(VLOOKUP(V1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,4)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>9484134.8908979744</v>
+        <v>5671979.4377256734</v>
       </c>
       <c r="W5" s="3">
         <f>(VLOOKUP(W1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,4)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>10224015.655168172</v>
+        <v>5959300.3926084824</v>
       </c>
       <c r="X5" s="3">
         <f>(VLOOKUP(X1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,4)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>10224015.655168172</v>
+        <v>5808073.770892201</v>
       </c>
       <c r="Y5" s="3">
         <f>(VLOOKUP(Y1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>10224015.655168172</v>
+        <v>5660684.7625884069</v>
       </c>
       <c r="Z5" s="3">
         <f>(VLOOKUP(Z1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>10224015.655168172</v>
+        <v>5517035.9822200155</v>
       </c>
       <c r="AA5" s="3">
         <f>(VLOOKUP(AA1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,4)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>10224015.655168172</v>
+        <v>5377032.5156196179</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4542,103 +4542,103 @@
       </c>
       <c r="C3" s="3">
         <f>VLOOKUP(C1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5227941.8581569847</v>
+        <v>4990515.6776992008</v>
       </c>
       <c r="D3" s="3">
         <f>VLOOKUP(D1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5358640.4046109095</v>
+        <v>4932757.1934147589</v>
       </c>
       <c r="E3" s="3">
         <f>VLOOKUP(E1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5489338.9510648344</v>
+        <v>4890066.1398132164</v>
       </c>
       <c r="F3" s="3">
         <f>VLOOKUP(F1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5620037.4975187592</v>
+        <v>4873971.3843110297</v>
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP(G1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5750736.0439726841</v>
+        <v>4866780.1105760103</v>
       </c>
       <c r="H3" s="3">
         <f>VLOOKUP(H1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>6168971.3926252434</v>
+        <v>5102197.3002760746</v>
       </c>
       <c r="I3" s="3">
         <f>VLOOKUP(I1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>6587206.7412778018</v>
+        <v>5333048.6018904131</v>
       </c>
       <c r="J3" s="3">
         <f>VLOOKUP(J1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>8763247.3662906531</v>
+        <v>6964676.9461349286</v>
       </c>
       <c r="K3" s="3">
         <f>VLOOKUP(K1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>10939287.991303504</v>
+        <v>8531689.2368856184</v>
       </c>
       <c r="L3" s="3">
         <f>VLOOKUP(L1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>13701263.724061584</v>
+        <v>10506296.549979102</v>
       </c>
       <c r="M3" s="3">
         <f>VLOOKUP(M1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>17937924.657013878</v>
+        <v>13520025.309172912</v>
       </c>
       <c r="N3" s="3">
         <f>VLOOKUP(N1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>19560614.660887685</v>
+        <v>14368937.408581555</v>
       </c>
       <c r="O3" s="3">
         <f>VLOOKUP(O1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>21444701.757669341</v>
+        <v>15353203.709059615</v>
       </c>
       <c r="P3" s="3">
         <f>VLOOKUP(P1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>23067391.761543147</v>
+        <v>16095865.684642907</v>
       </c>
       <c r="Q3" s="3">
         <f>VLOOKUP(Q1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>22805994.668635294</v>
+        <v>15509639.830210429</v>
       </c>
       <c r="R3" s="3">
         <f>VLOOKUP(R1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>23878736.822091162</v>
+        <v>15827083.348318409</v>
       </c>
       <c r="S3" s="3">
         <f>VLOOKUP(S1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>24951478.858324803</v>
+        <v>16118427.78356231</v>
       </c>
       <c r="T3" s="3">
         <f>VLOOKUP(T1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>26895544.65480683</v>
+        <v>16933376.959899783</v>
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>28839610.334066637</v>
+        <v>17696585.038355824</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>29972331.070000648</v>
+        <v>17924929.103750229</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>30233728.162908494</v>
+        <v>17622417.080334097</v>
       </c>
       <c r="X3" s="3">
         <f>VLOOKUP(X1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>30495125.255816344</v>
+        <v>17323715.369004481</v>
       </c>
       <c r="Y3" s="3">
         <f>VLOOKUP(Y1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>33100262.732829716</v>
+        <v>18326473.590118941</v>
       </c>
       <c r="Z3" s="3">
         <f>VLOOKUP(Z1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>35705400.186405391</v>
+        <v>19267182.703147344</v>
       </c>
       <c r="AA3" s="3">
         <f>VLOOKUP(AA1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>37138667.471366003</v>
+        <v>19532034.116103366</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4678,75 +4678,75 @@
       </c>
       <c r="J4" s="3">
         <f>(VLOOKUP(J1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,3)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>336974.1120065882</v>
+        <v>267813.48639824911</v>
       </c>
       <c r="K4" s="3">
         <f>(VLOOKUP(K1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,3)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>673948.2240131764</v>
+        <v>525620.75462337688</v>
       </c>
       <c r="L4" s="3">
         <f>(VLOOKUP(L1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,3)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1123247.0550540099</v>
+        <v>861319.57584054209</v>
       </c>
       <c r="M4" s="3">
         <f>(VLOOKUP(M1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,3)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1684870.5825810146</v>
+        <v>1269906.8233776556</v>
       </c>
       <c r="N4" s="3">
         <f>(VLOOKUP(N1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,3)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2246494.1101080198</v>
+        <v>1650241.2534834095</v>
       </c>
       <c r="O4" s="3">
         <f>(VLOOKUP(O1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,3)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2808117.6376350252</v>
+        <v>2010454.732213513</v>
       </c>
       <c r="P4" s="3">
         <f>(VLOOKUP(P1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,3)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3369741.1651620292</v>
+        <v>2351323.5370149044</v>
       </c>
       <c r="Q4" s="3">
         <f>(VLOOKUP(Q1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3369741.1651620292</v>
+        <v>2291655.0035229893</v>
       </c>
       <c r="R4" s="3">
         <f>(VLOOKUP(R1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,3)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3371447.0333769233</v>
+        <v>2234631.3207125673</v>
       </c>
       <c r="S4" s="3">
         <f>(VLOOKUP(S1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,3)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3630789.1016544555</v>
+        <v>2345456.6466643289</v>
       </c>
       <c r="T4" s="3">
         <f>(VLOOKUP(T1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,3)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3890131.1907561305</v>
+        <v>2449218.2152096475</v>
       </c>
       <c r="U4" s="3">
         <f>(VLOOKUP(U1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,3)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4149473.2590336637</v>
+        <v>2546203.1401350843</v>
       </c>
       <c r="V4" s="3">
         <f>(VLOOKUP(V1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,3)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4149473.2590336637</v>
+        <v>2481589.2301594075</v>
       </c>
       <c r="W4" s="3">
         <f>(VLOOKUP(W1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,3)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4149473.2590336637</v>
+        <v>2418614.9997900184</v>
       </c>
       <c r="X4" s="3">
         <f>(VLOOKUP(X1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,3)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4149473.2590336637</v>
+        <v>2357238.8395776157</v>
       </c>
       <c r="Y4" s="3">
         <f>(VLOOKUP(Y1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4564420.5932666864</v>
+        <v>2527162.2201877851</v>
       </c>
       <c r="Z4" s="3">
         <f>(VLOOKUP(Z1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4979367.9066755669</v>
+        <v>2686943.4512215443</v>
       </c>
       <c r="AA4" s="3">
         <f>(VLOOKUP(AA1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,3)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5186841.5737920795</v>
+        <v>2727872.9548452441</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4786,75 +4786,75 @@
       </c>
       <c r="J5" s="3">
         <f>(VLOOKUP(J1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,4)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>427095.09545021062</v>
+        <v>339438.02345824597</v>
       </c>
       <c r="K5" s="3">
         <f>(VLOOKUP(K1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,4)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>854190.19090042124</v>
+        <v>666193.74713893118</v>
       </c>
       <c r="L5" s="3">
         <f>(VLOOKUP(L1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,4)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1423650.3372196173</v>
+        <v>1091672.4856583616</v>
       </c>
       <c r="M5" s="3">
         <f>(VLOOKUP(M1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,4)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2135475.505829426</v>
+        <v>1609533.0668391217</v>
       </c>
       <c r="N5" s="3">
         <f>(VLOOKUP(N1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,4)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2847300.6744392347</v>
+        <v>2091584.8445312981</v>
       </c>
       <c r="O5" s="3">
         <f>(VLOOKUP(O1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,4)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3559125.8430490433</v>
+        <v>2548134.4861775921</v>
       </c>
       <c r="P5" s="3">
         <f>(VLOOKUP(P1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,4)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4270951.011658852</v>
+        <v>2980165.8783095884</v>
       </c>
       <c r="Q5" s="3">
         <f>(VLOOKUP(Q1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4270951.011658852</v>
+        <v>2904539.4812093703</v>
       </c>
       <c r="R5" s="3">
         <f>(VLOOKUP(R1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,4)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3836474.2103944304</v>
+        <v>2542856.330466025</v>
       </c>
       <c r="S5" s="3">
         <f>(VLOOKUP(S1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,4)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4131587.5984343807</v>
+        <v>2668967.9082732024</v>
       </c>
       <c r="T5" s="3">
         <f>(VLOOKUP(T1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,4)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4426701.0101707699</v>
+        <v>2787041.4173075301</v>
       </c>
       <c r="U5" s="3">
         <f>(VLOOKUP(U1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,4)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4721814.3982107211</v>
+        <v>2897403.573257165</v>
       </c>
       <c r="V5" s="3">
         <f>(VLOOKUP(V1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,4)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4721814.3982107211</v>
+        <v>2823877.3998365672</v>
       </c>
       <c r="W5" s="3">
         <f>(VLOOKUP(W1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,4)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4721814.3982107211</v>
+        <v>2752217.0687265731</v>
       </c>
       <c r="X5" s="3">
         <f>(VLOOKUP(X1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,4)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4721814.3982107211</v>
+        <v>2682375.2312434944</v>
       </c>
       <c r="Y5" s="3">
         <f>(VLOOKUP(Y1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5193995.8475103676</v>
+        <v>2875736.3195240316</v>
       </c>
       <c r="Z5" s="3">
         <f>(VLOOKUP(Z1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5666177.2731135776</v>
+        <v>3057556.3410452055</v>
       </c>
       <c r="AA5" s="3">
         <f>(VLOOKUP(AA1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,4)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5902267.9977634009</v>
+        <v>3104131.2934445883</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6321,11 +6321,11 @@
       </c>
       <c r="O7" s="22">
         <f>parameters!$G$7*(1-parameters!$H8)*parameters!L8/1000</f>
-        <v>1668976.2379441939</v>
+        <v>1593179.9371816625</v>
       </c>
       <c r="P7" s="22">
         <f>(G7+F7)*parameters!$C$7*parameters!L8/1000</f>
-        <v>703383.98959608329</v>
+        <v>671439.91321268037</v>
       </c>
       <c r="Q7" s="22">
         <f>E7*parameters!$E$7*parameters!$D$7*parameters!L8/1000</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="R7" s="24">
         <f t="shared" si="2"/>
-        <v>2372360.2275402769</v>
+        <v>2264619.850394343</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6385,11 +6385,11 @@
       </c>
       <c r="O8" s="22">
         <f>parameters!$G$7*(1-parameters!$H9)*parameters!L9/1000</f>
-        <v>2372059.5719482834</v>
+        <v>2183537.8068414764</v>
       </c>
       <c r="P8" s="22">
         <f>(G8+F8)*parameters!$C$7*parameters!L9/1000</f>
-        <v>1406767.9791921666</v>
+        <v>1294963.7118502564</v>
       </c>
       <c r="Q8" s="22">
         <f>E8*parameters!$E$7*parameters!$D$7*parameters!L9/1000</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="R8" s="24">
         <f t="shared" si="2"/>
-        <v>3778827.5511404499</v>
+        <v>3478501.5186917325</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6449,11 +6449,11 @@
       </c>
       <c r="O9" s="22">
         <f>parameters!$G$7*(1-parameters!$H10)*parameters!L10/1000</f>
-        <v>2372059.5719482834</v>
+        <v>2113101.1033949773</v>
       </c>
       <c r="P9" s="22">
         <f>(G9+F9)*parameters!$C$7*parameters!L10/1000</f>
-        <v>1406767.9791921666</v>
+        <v>1253190.6888873451</v>
       </c>
       <c r="Q9" s="22">
         <f>E9*parameters!$E$7*parameters!$D$7*parameters!L10/1000</f>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="R9" s="24">
         <f t="shared" si="2"/>
-        <v>3778827.5511404499</v>
+        <v>3366291.7922823224</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6513,11 +6513,11 @@
       </c>
       <c r="O10" s="22">
         <f>parameters!$G$7*(1-parameters!$H11)*parameters!L11/1000</f>
-        <v>2652480.0924470229</v>
+        <v>2300360.4644540558</v>
       </c>
       <c r="P10" s="22">
         <f>(G10+F10)*parameters!$C$7*parameters!L11/1000</f>
-        <v>1688121.5750305997</v>
+        <v>1464021.5930178044</v>
       </c>
       <c r="Q10" s="22">
         <f>E10*parameters!$E$7*parameters!$D$7*parameters!L11/1000</f>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="R10" s="24">
         <f t="shared" si="2"/>
-        <v>4340601.6674776226</v>
+        <v>3764382.0574718602</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6573,23 +6573,23 @@
       </c>
       <c r="N11" s="22">
         <f>E11*parameters!K12/1000</f>
-        <v>5225109.8925698651</v>
+        <v>4421948.8959827079</v>
       </c>
       <c r="O11" s="22">
         <f>parameters!$G$7*(1-parameters!$H12)*parameters!L12/1000</f>
-        <v>4845720.7817584276</v>
+        <v>4100876.3646497102</v>
       </c>
       <c r="P11" s="22">
         <f>(G11+F11)*parameters!$C$7*parameters!L12/1000</f>
-        <v>4389028.0657661734</v>
+        <v>3714382.7036920725</v>
       </c>
       <c r="Q11" s="22">
         <f>E11*parameters!$E$7*parameters!$D$7*parameters!L12/1000</f>
-        <v>4050873.6118249674</v>
+        <v>3428206.5762955411</v>
       </c>
       <c r="R11" s="24">
         <f t="shared" si="2"/>
-        <v>13285622.459349569</v>
+        <v>11243465.644637324</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6637,23 +6637,23 @@
       </c>
       <c r="N12" s="22">
         <f>E12*parameters!K13/1000</f>
-        <v>5225109.8925698651</v>
+        <v>4321553.7714093123</v>
       </c>
       <c r="O12" s="22">
         <f>parameters!$G$7*(1-parameters!$H13)*parameters!L13/1000</f>
-        <v>4845720.7817584276</v>
+        <v>4007770.8125111195</v>
       </c>
       <c r="P12" s="22">
         <f>(G12+F12)*parameters!$C$7*parameters!L13/1000</f>
-        <v>4389028.0657661734</v>
+        <v>3630052.0334328092</v>
       </c>
       <c r="Q12" s="22">
         <f>E12*parameters!$E$7*parameters!$D$7*parameters!L13/1000</f>
-        <v>4050873.6118249674</v>
+        <v>3350373.1968543623</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="2"/>
-        <v>13285622.459349569</v>
+        <v>10988196.042798292</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6701,23 +6701,23 @@
       </c>
       <c r="N13" s="22">
         <f>E13*parameters!K14/1000</f>
-        <v>7314234.1093765767</v>
+        <v>5921655.0387703823</v>
       </c>
       <c r="O13" s="22">
         <f>parameters!$G$7*(1-parameters!$H14)*parameters!L14/1000</f>
-        <v>4845720.7817584276</v>
+        <v>3923129.4014760382</v>
       </c>
       <c r="P13" s="22">
         <f>(G13+F13)*parameters!$C$7*parameters!L14/1000</f>
-        <v>3308461.7171749114</v>
+        <v>2678553.7221145355</v>
       </c>
       <c r="Q13" s="22">
         <f>E13*parameters!$E$7*parameters!$D$7*parameters!L14/1000</f>
-        <v>5670510.0090844641</v>
+        <v>4590884.5226386888</v>
       </c>
       <c r="R13" s="24">
         <f t="shared" si="2"/>
-        <v>13824692.508017804</v>
+        <v>11192567.646229263</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6765,23 +6765,23 @@
       </c>
       <c r="N14" s="22">
         <f>E14*parameters!K15/1000</f>
-        <v>12283961.088424752</v>
+        <v>9762798.7689663954</v>
       </c>
       <c r="O14" s="22">
         <f>parameters!$G$7*(1-parameters!$H15)*parameters!L15/1000</f>
-        <v>6334523.4485609187</v>
+        <v>5034424.7495112978</v>
       </c>
       <c r="P14" s="22">
         <f>(G14+F14)*parameters!$C$7*parameters!L15/1000</f>
-        <v>4409417.469920936</v>
+        <v>3504427.8581904382</v>
       </c>
       <c r="Q14" s="22">
         <f>E14*parameters!$E$7*parameters!$D$7*parameters!L15/1000</f>
-        <v>9523392.7792685535</v>
+        <v>7568809.9817767544</v>
       </c>
       <c r="R14" s="24">
         <f t="shared" si="2"/>
-        <v>20267333.697750408</v>
+        <v>16107662.589478489</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6829,23 +6829,23 @@
       </c>
       <c r="N15" s="22">
         <f>E15*parameters!K16/1000</f>
-        <v>12283961.088424752</v>
+        <v>9580416.8139417488</v>
       </c>
       <c r="O15" s="22">
         <f>parameters!$G$7*(1-parameters!$H16)*parameters!L16/1000</f>
-        <v>6334523.4485609187</v>
+        <v>4940375.0563885607</v>
       </c>
       <c r="P15" s="22">
         <f>(G15+F15)*parameters!$C$7*parameters!L16/1000</f>
-        <v>4409417.469920936</v>
+        <v>3438960.5245758919</v>
       </c>
       <c r="Q15" s="22">
         <f>E15*parameters!$E$7*parameters!$D$7*parameters!L16/1000</f>
-        <v>9523392.7792685535</v>
+        <v>7427414.6304688379</v>
       </c>
       <c r="R15" s="24">
         <f t="shared" si="2"/>
-        <v>20267333.697750408</v>
+        <v>15806750.211433291</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6893,23 +6893,23 @@
       </c>
       <c r="N16" s="22">
         <f>E16*parameters!K17/1000</f>
-        <v>18575042.429824498</v>
+        <v>14243569.653612144</v>
       </c>
       <c r="O16" s="22">
         <f>parameters!$G$7*(1-parameters!$H17)*parameters!L17/1000</f>
-        <v>7383052.3512953389</v>
+        <v>5661414.8161024535</v>
       </c>
       <c r="P16" s="22">
         <f>(G16+F16)*parameters!$C$7*parameters!L17/1000</f>
-        <v>5803096.0810412942</v>
+        <v>4449885.0298290467</v>
       </c>
       <c r="Q16" s="22">
         <f>E16*parameters!$E$7*parameters!$D$7*parameters!L17/1000</f>
-        <v>14400682.619996989</v>
+        <v>11042619.511229133</v>
       </c>
       <c r="R16" s="24">
         <f t="shared" si="2"/>
-        <v>27586831.052333623</v>
+        <v>21153919.357160635</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6957,23 +6957,23 @@
       </c>
       <c r="N17" s="22">
         <f>E17*parameters!K18/1000</f>
-        <v>22704384.382738147</v>
+        <v>17112562.20288473</v>
       </c>
       <c r="O17" s="22">
         <f>parameters!$G$7*(1-parameters!$H18)*parameters!L18/1000</f>
-        <v>8621237.6447052378</v>
+        <v>6497928.4605944296</v>
       </c>
       <c r="P17" s="22">
         <f>(G17+F17)*parameters!$C$7*parameters!L18/1000</f>
-        <v>6717879.2868958935</v>
+        <v>5063344.8249704437</v>
       </c>
       <c r="Q17" s="22">
         <f>E17*parameters!$E$7*parameters!$D$7*parameters!L18/1000</f>
-        <v>17602039.662275892</v>
+        <v>13266864.828422792</v>
       </c>
       <c r="R17" s="24">
         <f t="shared" si="2"/>
-        <v>32941156.593877025</v>
+        <v>24828138.113987666</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7021,23 +7021,23 @@
       </c>
       <c r="N18" s="22">
         <f>E18*parameters!K19/1000</f>
-        <v>26314279.048590593</v>
+        <v>19330079.098035254</v>
       </c>
       <c r="O18" s="22">
         <f>parameters!$G$7*(1-parameters!$H19)*parameters!L19/1000</f>
-        <v>9702279.0715554543</v>
+        <v>7127150.3026196016</v>
       </c>
       <c r="P18" s="22">
         <f>(G18+F18)*parameters!$C$7*parameters!L19/1000</f>
-        <v>7517588.0668616332</v>
+        <v>5522308.6937152687</v>
       </c>
       <c r="Q18" s="22">
         <f>E18*parameters!$E$7*parameters!$D$7*parameters!L19/1000</f>
-        <v>20400684.541336462</v>
+        <v>14986040.282917058</v>
       </c>
       <c r="R18" s="24">
         <f t="shared" si="2"/>
-        <v>37620551.679753549</v>
+        <v>27635499.279251926</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7085,23 +7085,23 @@
       </c>
       <c r="N19" s="22">
         <f>E19*parameters!K20/1000</f>
-        <v>26314279.048590593</v>
+        <v>18839547.933818366</v>
       </c>
       <c r="O19" s="22">
         <f>parameters!$G$7*(1-parameters!$H20)*parameters!L20/1000</f>
-        <v>9702279.0715554543</v>
+        <v>6946287.6523551187</v>
       </c>
       <c r="P19" s="22">
         <f>(G19+F19)*parameters!$C$7*parameters!L20/1000</f>
-        <v>7517588.0668616332</v>
+        <v>5382171.4237664603</v>
       </c>
       <c r="Q19" s="22">
         <f>E19*parameters!$E$7*parameters!$D$7*parameters!L20/1000</f>
-        <v>20400684.541336462</v>
+        <v>14605745.937006822</v>
       </c>
       <c r="R19" s="24">
         <f t="shared" si="2"/>
-        <v>37620551.679753549</v>
+        <v>26934205.0131284</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7149,23 +7149,23 @@
       </c>
       <c r="N20" s="22">
         <f>E20*parameters!K21/1000</f>
-        <v>26314279.048590593</v>
+        <v>18361464.769521583</v>
       </c>
       <c r="O20" s="22">
         <f>parameters!$G$7*(1-parameters!$H21)*parameters!L21/1000</f>
-        <v>9702279.0715554543</v>
+        <v>6770014.6763463719</v>
       </c>
       <c r="P20" s="22">
         <f>(G20+F20)*parameters!$C$7*parameters!L21/1000</f>
-        <v>7517588.0668616332</v>
+        <v>5245590.3574849796</v>
       </c>
       <c r="Q20" s="22">
         <f>E20*parameters!$E$7*parameters!$D$7*parameters!L21/1000</f>
-        <v>20400684.541336462</v>
+        <v>14235102.158344569</v>
       </c>
       <c r="R20" s="24">
         <f t="shared" si="2"/>
-        <v>37620551.679753549</v>
+        <v>26250707.192175917</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7213,23 +7213,23 @@
       </c>
       <c r="N21" s="22">
         <f>E21*parameters!K22/1000</f>
-        <v>29483430.408774905</v>
+        <v>20050753.902352631</v>
       </c>
       <c r="O21" s="22">
         <f>parameters!$G$7*(1-parameters!$H22)*parameters!L22/1000</f>
-        <v>10651915.713437662</v>
+        <v>7244032.9228167385</v>
       </c>
       <c r="P21" s="22">
         <f>(G21+F21)*parameters!$C$7*parameters!L22/1000</f>
-        <v>8219657.9061158728</v>
+        <v>5589930.8714092309</v>
       </c>
       <c r="Q21" s="22">
         <f>E21*parameters!$E$7*parameters!$D$7*parameters!L22/1000</f>
-        <v>22857634.132981472</v>
+        <v>15544758.206087964</v>
       </c>
       <c r="R21" s="24">
         <f t="shared" si="2"/>
-        <v>41729207.752535008</v>
+        <v>28378722.00031393</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7277,23 +7277,23 @@
       </c>
       <c r="N22" s="22">
         <f>E22*parameters!K23/1000</f>
-        <v>29483430.408774905</v>
+        <v>19541934.481321543</v>
       </c>
       <c r="O22" s="22">
         <f>parameters!$G$7*(1-parameters!$H23)*parameters!L23/1000</f>
-        <v>10651915.713437662</v>
+        <v>7060204.1922030114</v>
       </c>
       <c r="P22" s="22">
         <f>(G22+F22)*parameters!$C$7*parameters!L23/1000</f>
-        <v>8219657.9061158728</v>
+        <v>5448077.5823286399</v>
       </c>
       <c r="Q22" s="22">
         <f>E22*parameters!$E$7*parameters!$D$7*parameters!L23/1000</f>
-        <v>22857634.132981472</v>
+        <v>15150285.513988251</v>
       </c>
       <c r="R22" s="24">
         <f t="shared" si="2"/>
-        <v>41729207.752535008</v>
+        <v>27658567.288519904</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7341,23 +7341,23 @@
       </c>
       <c r="N23" s="22">
         <f>E23*parameters!K24/1000</f>
-        <v>32981390.411105335</v>
+        <v>21305677.4134055</v>
       </c>
       <c r="O23" s="22">
         <f>parameters!$G$7*(1-parameters!$H24)*parameters!L24/1000</f>
-        <v>11700444.616172083</v>
+        <v>7558380.5133224837</v>
       </c>
       <c r="P23" s="22">
         <f>(G23+F23)*parameters!$C$7*parameters!L24/1000</f>
-        <v>8994569.5267495625</v>
+        <v>5810409.8832912473</v>
       </c>
       <c r="Q23" s="22">
         <f>E23*parameters!$E$7*parameters!$D$7*parameters!L24/1000</f>
-        <v>25569499.368353661</v>
+        <v>16517663.396658521</v>
       </c>
       <c r="R23" s="24">
         <f t="shared" si="2"/>
-        <v>46264513.511275306</v>
+        <v>29886453.793272253</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7405,23 +7405,23 @@
       </c>
       <c r="N24" s="22">
         <f>E24*parameters!K25/1000</f>
-        <v>32981390.411105335</v>
+        <v>20765012.334228996</v>
       </c>
       <c r="O24" s="22">
         <f>parameters!$G$7*(1-parameters!$H25)*parameters!L25/1000</f>
-        <v>11700444.616172083</v>
+        <v>7366574.7181164427</v>
       </c>
       <c r="P24" s="22">
         <f>(G24+F24)*parameters!$C$7*parameters!L25/1000</f>
-        <v>8994569.5267495625</v>
+        <v>5662961.592460514</v>
       </c>
       <c r="Q24" s="22">
         <f>E24*parameters!$E$7*parameters!$D$7*parameters!L25/1000</f>
-        <v>25569499.368353661</v>
+        <v>16098501.704923429</v>
       </c>
       <c r="R24" s="24">
         <f t="shared" si="2"/>
-        <v>46264513.511275306</v>
+        <v>29128038.015500385</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7469,23 +7469,23 @@
       </c>
       <c r="N25" s="22">
         <f>E25*parameters!K26/1000</f>
-        <v>36307950.743942745</v>
+        <v>22279314.126156405</v>
       </c>
       <c r="O25" s="22">
         <f>parameters!$G$7*(1-parameters!$H26)*parameters!L26/1000</f>
-        <v>12697495.355723159</v>
+        <v>7791447.3785817642</v>
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
-        <v>9731510.5600768086</v>
+        <v>5971457.3873638483</v>
       </c>
       <c r="Q25" s="22">
         <f>E25*parameters!$E$7*parameters!$D$7*parameters!L26/1000</f>
-        <v>28148483.494524274</v>
+        <v>17272495.227620617</v>
       </c>
       <c r="R25" s="24">
         <f t="shared" si="2"/>
-        <v>50577489.410324246</v>
+        <v>31035399.99356623</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7533,23 +7533,23 @@
       </c>
       <c r="N26" s="22">
         <f>E26*parameters!K27/1000</f>
-        <v>36307950.743942745</v>
+        <v>21713941.483818486</v>
       </c>
       <c r="O26" s="22">
         <f>parameters!$G$7*(1-parameters!$H27)*parameters!L27/1000</f>
-        <v>12697495.355723159</v>
+        <v>7593727.1450448623</v>
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
-        <v>9731510.5600768086</v>
+        <v>5819922.2627821369</v>
       </c>
       <c r="Q26" s="22">
         <f>E26*parameters!$E$7*parameters!$D$7*parameters!L27/1000</f>
-        <v>28148483.494524274</v>
+        <v>16834178.490789644</v>
       </c>
       <c r="R26" s="24">
         <f t="shared" si="2"/>
-        <v>50577489.410324246</v>
+        <v>30247827.898616642</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7597,23 +7597,23 @@
       </c>
       <c r="N27" s="22">
         <f>E27*parameters!K28/1000</f>
-        <v>39140423.568775117</v>
+        <v>22813887.361602169</v>
       </c>
       <c r="O27" s="22">
         <f>parameters!$G$7*(1-parameters!$H28)*parameters!L28/1000</f>
-        <v>13546885.048248328</v>
+        <v>7896110.5019278638</v>
       </c>
       <c r="P27" s="22">
         <f>(G27+F27)*parameters!$C$7*parameters!L28/1000</f>
-        <v>10358995.181293016</v>
+        <v>6037976.2837807843</v>
       </c>
       <c r="Q27" s="22">
         <f>E27*parameters!$E$7*parameters!$D$7*parameters!L28/1000</f>
-        <v>30344416.146321874</v>
+        <v>17686934.092559028</v>
       </c>
       <c r="R27" s="24">
         <f t="shared" si="2"/>
-        <v>54250296.375863224</v>
+        <v>31621020.878267676</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7661,23 +7661,23 @@
       </c>
       <c r="N28" s="22">
         <f>E28*parameters!K29/1000</f>
-        <v>39140423.568775117</v>
+        <v>22234949.082506504</v>
       </c>
       <c r="O28" s="22">
         <f>parameters!$G$7*(1-parameters!$H29)*parameters!L29/1000</f>
-        <v>13546885.048248328</v>
+        <v>7695734.2769961432</v>
       </c>
       <c r="P28" s="22">
         <f>(G28+F28)*parameters!$C$7*parameters!L29/1000</f>
-        <v>10358995.181293016</v>
+        <v>5884753.1375652067</v>
       </c>
       <c r="Q28" s="22">
         <f>E28*parameters!$E$7*parameters!$D$7*parameters!L29/1000</f>
-        <v>30344416.146321874</v>
+        <v>17238100.317598835</v>
       </c>
       <c r="R28" s="24">
         <f t="shared" si="2"/>
-        <v>54250296.375863224</v>
+        <v>30818587.732160185</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7725,23 +7725,23 @@
       </c>
       <c r="N29" s="22">
         <f>E29*parameters!K30/1000</f>
-        <v>39140423.568775117</v>
+        <v>21670702.272939455</v>
       </c>
       <c r="O29" s="22">
         <f>parameters!$G$7*(1-parameters!$H30)*parameters!L30/1000</f>
-        <v>13546885.048248328</v>
+        <v>7500442.9139730902</v>
       </c>
       <c r="P29" s="22">
         <f>(G29+F29)*parameters!$C$7*parameters!L30/1000</f>
-        <v>10358995.181293016</v>
+        <v>5735418.2697119107</v>
       </c>
       <c r="Q29" s="22">
         <f>E29*parameters!$E$7*parameters!$D$7*parameters!L30/1000</f>
-        <v>30344416.146321874</v>
+        <v>16800656.405714441</v>
       </c>
       <c r="R29" s="24">
         <f t="shared" si="2"/>
-        <v>54250296.375863224</v>
+        <v>30036517.589399442</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7789,23 +7789,23 @@
       </c>
       <c r="N30" s="22">
         <f>E30*parameters!K31/1000</f>
-        <v>39140423.568775117</v>
+        <v>21120774.113751374</v>
       </c>
       <c r="O30" s="22">
         <f>parameters!$G$7*(1-parameters!$H31)*parameters!L31/1000</f>
-        <v>13546885.048248328</v>
+        <v>7310107.3764890507</v>
       </c>
       <c r="P30" s="22">
         <f>(G30+F30)*parameters!$C$7*parameters!L31/1000</f>
-        <v>10358995.181293016</v>
+        <v>5589873.0090410151</v>
       </c>
       <c r="Q30" s="22">
         <f>E30*parameters!$E$7*parameters!$D$7*parameters!L31/1000</f>
-        <v>30344416.146321874</v>
+        <v>16374313.321213527</v>
       </c>
       <c r="R30" s="24">
         <f t="shared" si="2"/>
-        <v>54250296.375863224</v>
+        <v>29274293.706743591</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7853,23 +7853,23 @@
       </c>
       <c r="N31" s="26">
         <f>E31*parameters!K32/1000</f>
-        <v>39140423.568775125</v>
+        <v>20584801.246665001</v>
       </c>
       <c r="O31" s="22">
         <f>parameters!$G$7*(1-parameters!$H32)*parameters!L32/1000</f>
-        <v>13546885.048248328</v>
+        <v>7124601.9026752319</v>
       </c>
       <c r="P31" s="22">
         <f>(G31+F31)*parameters!$C$7*parameters!L32/1000</f>
-        <v>10358995.181293016</v>
+        <v>5448021.1883090371</v>
       </c>
       <c r="Q31" s="22">
         <f>E31*parameters!$E$7*parameters!$D$7*parameters!L32/1000</f>
-        <v>30344416.146321878</v>
+        <v>15958789.363139125</v>
       </c>
       <c r="R31" s="27">
         <f t="shared" si="2"/>
-        <v>54250296.375863224</v>
+        <v>28531412.454123393</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9172,11 +9172,11 @@
       </c>
       <c r="O7" s="22">
         <f>parameters!$G$7*(1-parameters!$I8)*parameters!L8/1000</f>
-        <v>2709377.0096496656</v>
+        <v>2586331.0668533486</v>
       </c>
       <c r="P7" s="22">
         <f>(G7+F7)*parameters!$C$7*parameters!L8/1000</f>
-        <v>2518564.8485073196</v>
+        <v>2404184.6108458517</v>
       </c>
       <c r="Q7" s="22">
         <f>E7*parameters!$E$7*parameters!$D$7*parameters!L8/1000</f>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="R7" s="24">
         <f>O7+P7+Q6</f>
-        <v>5227941.8581569847</v>
+        <v>4990515.6776992008</v>
       </c>
       <c r="S7" s="5"/>
     </row>
@@ -9235,11 +9235,11 @@
       </c>
       <c r="O8" s="22">
         <f>parameters!$G$7*(1-parameters!$I9)*parameters!L9/1000</f>
-        <v>2777111.4348909073</v>
+        <v>2556397.7750000143</v>
       </c>
       <c r="P8" s="22">
         <f>(G8+F8)*parameters!$C$7*parameters!L9/1000</f>
-        <v>2581528.9697200027</v>
+        <v>2376359.418414745</v>
       </c>
       <c r="Q8" s="22">
         <f>E8*parameters!$E$7*parameters!$D$7*parameters!L9/1000</f>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="R8" s="24">
         <f t="shared" ref="R8:R31" si="4">O8+P8+Q8</f>
-        <v>5358640.4046109095</v>
+        <v>4932757.1934147589</v>
       </c>
       <c r="S8" s="5"/>
     </row>
@@ -9298,11 +9298,11 @@
       </c>
       <c r="O9" s="22">
         <f>parameters!$G$7*(1-parameters!$I10)*parameters!L10/1000</f>
-        <v>2844845.860132149</v>
+        <v>2534273.1679779845</v>
       </c>
       <c r="P9" s="22">
         <f>(G9+F9)*parameters!$C$7*parameters!L10/1000</f>
-        <v>2644493.0909326854</v>
+        <v>2355792.9718352314</v>
       </c>
       <c r="Q9" s="22">
         <f>E9*parameters!$E$7*parameters!$D$7*parameters!L10/1000</f>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="R9" s="24">
         <f t="shared" si="4"/>
-        <v>5489338.9510648344</v>
+        <v>4890066.1398132164</v>
       </c>
       <c r="S9" s="5"/>
     </row>
@@ -9361,11 +9361,11 @@
       </c>
       <c r="O10" s="22">
         <f>parameters!$G$7*(1-parameters!$I11)*parameters!L11/1000</f>
-        <v>2912580.2853733902</v>
+        <v>2525932.0728172725</v>
       </c>
       <c r="P10" s="22">
         <f>(G10+F10)*parameters!$C$7*parameters!L11/1000</f>
-        <v>2707457.2121453686</v>
+        <v>2348039.3114937567</v>
       </c>
       <c r="Q10" s="22">
         <f>E10*parameters!$E$7*parameters!$D$7*parameters!L11/1000</f>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="R10" s="24">
         <f t="shared" si="4"/>
-        <v>5620037.4975187592</v>
+        <v>4873971.3843110297</v>
       </c>
       <c r="S10" s="5"/>
     </row>
@@ -9424,11 +9424,11 @@
       </c>
       <c r="O11" s="22">
         <f>parameters!$G$7*(1-parameters!$I12)*parameters!L12/1000</f>
-        <v>2980314.7106146323</v>
+        <v>2522205.2005114229</v>
       </c>
       <c r="P11" s="22">
         <f>(G11+F11)*parameters!$C$7*parameters!L12/1000</f>
-        <v>2770421.3333580513</v>
+        <v>2344574.9100645874</v>
       </c>
       <c r="Q11" s="22">
         <f>E11*parameters!$E$7*parameters!$D$7*parameters!L12/1000</f>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="R11" s="24">
         <f t="shared" si="4"/>
-        <v>5750736.0439726841</v>
+        <v>4866780.1105760103</v>
       </c>
       <c r="S11" s="5"/>
     </row>
@@ -9487,11 +9487,11 @@
       </c>
       <c r="O12" s="22">
         <f>parameters!$G$7*(1-parameters!$I13)*parameters!L13/1000</f>
-        <v>3197064.8713866058</v>
+        <v>2644209.985330232</v>
       </c>
       <c r="P12" s="22">
         <f>(G12+F12)*parameters!$C$7*parameters!L13/1000</f>
-        <v>2971906.5212386376</v>
+        <v>2457987.3149458426</v>
       </c>
       <c r="Q12" s="22">
         <f>E12*parameters!$E$7*parameters!$D$7*parameters!L13/1000</f>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
-        <v>6168971.3926252434</v>
+        <v>5102197.3002760746</v>
       </c>
       <c r="S12" s="5"/>
     </row>
@@ -9550,11 +9550,11 @@
       </c>
       <c r="O13" s="22">
         <f>parameters!$G$7*(1-parameters!$I14)*parameters!L14/1000</f>
-        <v>3413815.0321585792</v>
+        <v>2763848.5020183437</v>
       </c>
       <c r="P13" s="22">
         <f>(G13+F13)*parameters!$C$7*parameters!L14/1000</f>
-        <v>3173391.7091192226</v>
+        <v>2569200.0998720699</v>
       </c>
       <c r="Q13" s="22">
         <f>E13*parameters!$E$7*parameters!$D$7*parameters!L14/1000</f>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="R13" s="24">
         <f t="shared" si="4"/>
-        <v>6587206.7412778018</v>
+        <v>5333048.6018904131</v>
       </c>
       <c r="S13" s="5"/>
     </row>
@@ -9609,23 +9609,23 @@
       </c>
       <c r="N14" s="22">
         <f>E14*parameters!K15/1000</f>
-        <v>1355733.0552823199</v>
+        <v>1077482.1662069091</v>
       </c>
       <c r="O14" s="22">
         <f>parameters!$G$7*(1-parameters!$I15)*parameters!L15/1000</f>
-        <v>4036971.7443780014</v>
+        <v>3208422.9584139576</v>
       </c>
       <c r="P14" s="22">
         <f>(G14+F14)*parameters!$C$7*parameters!L15/1000</f>
-        <v>3675215.7645627595</v>
+        <v>2920913.8390848129</v>
       </c>
       <c r="Q14" s="22">
         <f>E14*parameters!$E$7*parameters!$D$7*parameters!L15/1000</f>
-        <v>1051059.8573498917</v>
+        <v>835340.14863615844</v>
       </c>
       <c r="R14" s="24">
         <f t="shared" si="4"/>
-        <v>8763247.3662906531</v>
+        <v>6964676.9461349286</v>
       </c>
       <c r="S14" s="5"/>
     </row>
@@ -9672,23 +9672,23 @@
       </c>
       <c r="N15" s="22">
         <f>E15*parameters!K16/1000</f>
-        <v>2711466.1105646398</v>
+        <v>2114706.7569731208</v>
       </c>
       <c r="O15" s="22">
         <f>parameters!$G$7*(1-parameters!$I16)*parameters!L16/1000</f>
-        <v>4660128.456597426</v>
+        <v>3634493.198027513</v>
       </c>
       <c r="P15" s="22">
         <f>(G15+F15)*parameters!$C$7*parameters!L16/1000</f>
-        <v>4177039.820006296</v>
+        <v>3257726.2526337323</v>
       </c>
       <c r="Q15" s="22">
         <f>E15*parameters!$E$7*parameters!$D$7*parameters!L16/1000</f>
-        <v>2102119.7146997834</v>
+        <v>1639469.7862243729</v>
       </c>
       <c r="R15" s="24">
         <f t="shared" si="4"/>
-        <v>10939287.991303504</v>
+        <v>8531689.2368856184</v>
       </c>
       <c r="S15" s="5"/>
     </row>
@@ -9735,23 +9735,23 @@
       </c>
       <c r="N16" s="22">
         <f>E16*parameters!K17/1000</f>
-        <v>4519110.2447521798</v>
+        <v>3465308.9911724133</v>
       </c>
       <c r="O16" s="22">
         <f>parameters!$G$7*(1-parameters!$I17)*parameters!L17/1000</f>
-        <v>5418754.019299333</v>
+        <v>4155166.8375063888</v>
       </c>
       <c r="P16" s="22">
         <f>(G16+F16)*parameters!$C$7*parameters!L17/1000</f>
-        <v>4778976.8000426395</v>
+        <v>3664577.8431768022</v>
       </c>
       <c r="Q16" s="22">
         <f>E16*parameters!$E$7*parameters!$D$7*parameters!L17/1000</f>
-        <v>3503532.9047196112</v>
+        <v>2686551.8692959119</v>
       </c>
       <c r="R16" s="24">
         <f t="shared" si="4"/>
-        <v>13701263.724061584</v>
+        <v>10506296.549979102</v>
       </c>
       <c r="S16" s="5"/>
     </row>
@@ -9798,23 +9798,23 @@
       </c>
       <c r="N17" s="22">
         <f>E17*parameters!K18/1000</f>
-        <v>6778665.3671282688</v>
+        <v>5109160.0103333583</v>
       </c>
       <c r="O17" s="22">
         <f>parameters!$G$7*(1-parameters!$I18)*parameters!L18/1000</f>
-        <v>6773442.5241241641</v>
+        <v>5105223.4919817951</v>
       </c>
       <c r="P17" s="22">
         <f>(G17+F17)*parameters!$C$7*parameters!L18/1000</f>
-        <v>5909182.7758102985</v>
+        <v>4453820.7297155373</v>
       </c>
       <c r="Q17" s="22">
         <f>E17*parameters!$E$7*parameters!$D$7*parameters!L18/1000</f>
-        <v>5255299.3570794165</v>
+        <v>3960981.0874755788</v>
       </c>
       <c r="R17" s="24">
         <f t="shared" si="4"/>
-        <v>17937924.657013878</v>
+        <v>13520025.309172912</v>
       </c>
       <c r="S17" s="5"/>
     </row>
@@ -9861,23 +9861,23 @@
       </c>
       <c r="N18" s="22">
         <f>E18*parameters!K19/1000</f>
-        <v>9038220.4895043597</v>
+        <v>6639342.7175030187</v>
       </c>
       <c r="O18" s="22">
         <f>parameters!$G$7*(1-parameters!$I19)*parameters!L19/1000</f>
-        <v>6773442.5241241641</v>
+        <v>4975670.4151211958</v>
       </c>
       <c r="P18" s="22">
         <f>(G18+F18)*parameters!$C$7*parameters!L19/1000</f>
-        <v>5780106.3273242991</v>
+        <v>4245980.3780266261</v>
       </c>
       <c r="Q18" s="22">
         <f>E18*parameters!$E$7*parameters!$D$7*parameters!L19/1000</f>
-        <v>7007065.8094392223</v>
+        <v>5147286.615433733</v>
       </c>
       <c r="R18" s="24">
         <f t="shared" si="4"/>
-        <v>19560614.660887685</v>
+        <v>14368937.408581555</v>
       </c>
       <c r="S18" s="5"/>
     </row>
@@ -9924,23 +9924,23 @@
       </c>
       <c r="N19" s="22">
         <f>E19*parameters!K20/1000</f>
-        <v>11297775.61188045</v>
+        <v>8088573.6900683194</v>
       </c>
       <c r="O19" s="22">
         <f>parameters!$G$7*(1-parameters!$I20)*parameters!L20/1000</f>
-        <v>6908911.3746066485</v>
+        <v>4946393.0504064653</v>
       </c>
       <c r="P19" s="22">
         <f>(G19+F19)*parameters!$C$7*parameters!L20/1000</f>
-        <v>5776958.1212636642</v>
+        <v>4135978.0078427587</v>
       </c>
       <c r="Q19" s="22">
         <f>E19*parameters!$E$7*parameters!$D$7*parameters!L20/1000</f>
-        <v>8758832.2617990281</v>
+        <v>6270832.6508103898</v>
       </c>
       <c r="R19" s="24">
         <f t="shared" si="4"/>
-        <v>21444701.757669341</v>
+        <v>15353203.709059615</v>
       </c>
       <c r="S19" s="5"/>
     </row>
@@ -9987,23 +9987,23 @@
       </c>
       <c r="N20" s="22">
         <f>E20*parameters!K21/1000</f>
-        <v>13557330.734256538</v>
+        <v>9459976.0907808952</v>
       </c>
       <c r="O20" s="22">
         <f>parameters!$G$7*(1-parameters!$I21)*parameters!L21/1000</f>
-        <v>6908911.3746066485</v>
+        <v>4820870.5458484357</v>
       </c>
       <c r="P20" s="22">
         <f>(G20+F20)*parameters!$C$7*parameters!L21/1000</f>
-        <v>5647881.6727776639</v>
+        <v>3940954.6492092926</v>
       </c>
       <c r="Q20" s="22">
         <f>E20*parameters!$E$7*parameters!$D$7*parameters!L21/1000</f>
-        <v>10510598.714158833</v>
+        <v>7334040.4895851789</v>
       </c>
       <c r="R20" s="24">
         <f t="shared" si="4"/>
-        <v>23067391.761543147</v>
+        <v>16095865.684642907</v>
       </c>
       <c r="S20" s="5"/>
     </row>
@@ -10050,23 +10050,23 @@
       </c>
       <c r="N21" s="22">
         <f>E21*parameters!K22/1000</f>
-        <v>13557330.734256538</v>
+        <v>9219914.3164994679</v>
       </c>
       <c r="O21" s="22">
         <f>parameters!$G$7*(1-parameters!$I22)*parameters!L22/1000</f>
-        <v>6773442.5241241641</v>
+        <v>4606405.2669571014</v>
       </c>
       <c r="P21" s="22">
         <f>(G21+F21)*parameters!$C$7*parameters!L22/1000</f>
-        <v>5521953.4303522985</v>
+        <v>3755306.8878746689</v>
       </c>
       <c r="Q21" s="22">
         <f>E21*parameters!$E$7*parameters!$D$7*parameters!L22/1000</f>
-        <v>10510598.714158833</v>
+        <v>7147927.6753786569</v>
       </c>
       <c r="R21" s="24">
         <f t="shared" si="4"/>
-        <v>22805994.668635294</v>
+        <v>15509639.830210429</v>
       </c>
       <c r="S21" s="5"/>
     </row>
@@ -10113,23 +10113,23 @@
       </c>
       <c r="N22" s="22">
         <f>E22*parameters!K23/1000</f>
-        <v>14687108.340802919</v>
+        <v>9734773.2247133683</v>
       </c>
       <c r="O22" s="22">
         <f>parameters!$G$7*(1-parameters!$I23)*parameters!L23/1000</f>
-        <v>6908911.3746066485</v>
+        <v>4579300.6969649447</v>
       </c>
       <c r="P22" s="22">
         <f>(G22+F22)*parameters!$C$7*parameters!L23/1000</f>
-        <v>5583343.4719807971</v>
+        <v>3700700.0475660339</v>
       </c>
       <c r="Q22" s="22">
         <f>E22*parameters!$E$7*parameters!$D$7*parameters!L23/1000</f>
-        <v>11386481.975503715</v>
+        <v>7547082.6037874306</v>
       </c>
       <c r="R22" s="24">
         <f t="shared" si="4"/>
-        <v>23878736.822091162</v>
+        <v>15827083.348318409</v>
       </c>
       <c r="S22" s="5"/>
     </row>
@@ -10176,23 +10176,23 @@
       </c>
       <c r="N23" s="22">
         <f>E23*parameters!K24/1000</f>
-        <v>15816885.856632629</v>
+        <v>10217564.012480238</v>
       </c>
       <c r="O23" s="22">
         <f>parameters!$G$7*(1-parameters!$I24)*parameters!L24/1000</f>
-        <v>7044380.2250891319</v>
+        <v>4550605.380256677</v>
       </c>
       <c r="P23" s="22">
         <f>(G23+F23)*parameters!$C$7*parameters!L24/1000</f>
-        <v>5644733.4667170309</v>
+        <v>3646446.3392068571</v>
       </c>
       <c r="Q23" s="22">
         <f>E23*parameters!$E$7*parameters!$D$7*parameters!L24/1000</f>
-        <v>12262365.16651864</v>
+        <v>7921376.0640987745</v>
       </c>
       <c r="R23" s="24">
         <f t="shared" si="4"/>
-        <v>24951478.858324803</v>
+        <v>16118427.78356231</v>
       </c>
       <c r="S23" s="5"/>
     </row>
@@ -10239,23 +10239,23 @@
       </c>
       <c r="N24" s="22">
         <f>E24*parameters!K25/1000</f>
-        <v>16946663.463179007</v>
+        <v>10669582.799591454</v>
       </c>
       <c r="O24" s="22">
         <f>parameters!$G$7*(1-parameters!$I25)*parameters!L25/1000</f>
-        <v>7631411.9105132269</v>
+        <v>4804720.4946226655</v>
       </c>
       <c r="P24" s="22">
         <f>(G24+F24)*parameters!$C$7*parameters!L25/1000</f>
-        <v>6125884.3164300825</v>
+        <v>3856843.5655126027</v>
       </c>
       <c r="Q24" s="22">
         <f>E24*parameters!$E$7*parameters!$D$7*parameters!L25/1000</f>
-        <v>13138248.427863522</v>
+        <v>8271812.8997645164</v>
       </c>
       <c r="R24" s="24">
         <f t="shared" si="4"/>
-        <v>26895544.65480683</v>
+        <v>16933376.959899783</v>
       </c>
       <c r="S24" s="5"/>
     </row>
@@ -10302,23 +10302,23 @@
       </c>
       <c r="N25" s="22">
         <f>E25*parameters!K26/1000</f>
-        <v>18076440.979008719</v>
+        <v>11092080.346105712</v>
       </c>
       <c r="O25" s="22">
         <f>parameters!$G$7*(1-parameters!$I26)*parameters!L26/1000</f>
-        <v>8218443.595937321</v>
+        <v>5043008.0120270317</v>
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
-        <v>6607035.1192508684</v>
+        <v>4054214.2381553957</v>
       </c>
       <c r="Q25" s="22">
         <f>E25*parameters!$E$7*parameters!$D$7*parameters!L26/1000</f>
-        <v>14014131.618878445</v>
+        <v>8599362.7881733961</v>
       </c>
       <c r="R25" s="24">
         <f t="shared" si="4"/>
-        <v>28839610.334066637</v>
+        <v>17696585.038355824</v>
       </c>
       <c r="S25" s="5"/>
     </row>
@@ -10365,23 +10365,23 @@
       </c>
       <c r="N26" s="22">
         <f>E26*parameters!K27/1000</f>
-        <v>18076440.979008719</v>
+        <v>10810601.358970294</v>
       </c>
       <c r="O26" s="22">
         <f>parameters!$G$7*(1-parameters!$I27)*parameters!L27/1000</f>
-        <v>8805475.2813614141</v>
+        <v>5266107.5901836781</v>
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
-        <v>7152724.1697607879</v>
+        <v>4277681.083336575</v>
       </c>
       <c r="Q26" s="22">
         <f>E26*parameters!$E$7*parameters!$D$7*parameters!L27/1000</f>
-        <v>14014131.618878445</v>
+        <v>8381140.4302299777</v>
       </c>
       <c r="R26" s="24">
         <f t="shared" si="4"/>
-        <v>29972331.070000648</v>
+        <v>17924929.103750229</v>
       </c>
       <c r="S26" s="5"/>
     </row>
@@ -10428,23 +10428,23 @@
       </c>
       <c r="N27" s="22">
         <f>E27*parameters!K28/1000</f>
-        <v>18076440.979008719</v>
+        <v>10536265.34391284</v>
       </c>
       <c r="O27" s="22">
         <f>parameters!$G$7*(1-parameters!$I28)*parameters!L28/1000</f>
-        <v>8940944.1318438966</v>
+        <v>5211432.9312723894</v>
       </c>
       <c r="P27" s="22">
         <f>(G27+F27)*parameters!$C$7*parameters!L28/1000</f>
-        <v>7278652.4121861542</v>
+        <v>4242528.3411685247</v>
       </c>
       <c r="Q27" s="22">
         <f>E27*parameters!$E$7*parameters!$D$7*parameters!L28/1000</f>
-        <v>14014131.618878445</v>
+        <v>8168455.8078931849</v>
       </c>
       <c r="R27" s="24">
         <f t="shared" si="4"/>
-        <v>30233728.162908494</v>
+        <v>17622417.080334097</v>
       </c>
       <c r="S27" s="5"/>
     </row>
@@ -10491,23 +10491,23 @@
       </c>
       <c r="N28" s="22">
         <f>E28*parameters!K29/1000</f>
-        <v>18076440.979008719</v>
+        <v>10268891.03678065</v>
       </c>
       <c r="O28" s="22">
         <f>parameters!$G$7*(1-parameters!$I29)*parameters!L29/1000</f>
-        <v>9076412.982326379</v>
+        <v>5156141.9655874157</v>
       </c>
       <c r="P28" s="22">
         <f>(G28+F28)*parameters!$C$7*parameters!L29/1000</f>
-        <v>7404580.6546115205</v>
+        <v>4206405.0110061755</v>
       </c>
       <c r="Q28" s="22">
         <f>E28*parameters!$E$7*parameters!$D$7*parameters!L29/1000</f>
-        <v>14014131.618878445</v>
+        <v>7961168.3924108902</v>
       </c>
       <c r="R28" s="24">
         <f t="shared" si="4"/>
-        <v>30495125.255816344</v>
+        <v>17323715.369004481</v>
       </c>
       <c r="S28" s="5"/>
     </row>
@@ -10554,23 +10554,23 @@
       </c>
       <c r="N29" s="22">
         <f>E29*parameters!K30/1000</f>
-        <v>19884085.113196258</v>
+        <v>11009131.97070311</v>
       </c>
       <c r="O29" s="22">
         <f>parameters!$G$7*(1-parameters!$I30)*parameters!L30/1000</f>
-        <v>9753757.2347387988</v>
+        <v>5400318.8980606254</v>
       </c>
       <c r="P29" s="22">
         <f>(G29+F29)*parameters!$C$7*parameters!L30/1000</f>
-        <v>7930960.6891926434</v>
+        <v>4391099.3331965897</v>
       </c>
       <c r="Q29" s="22">
         <f>E29*parameters!$E$7*parameters!$D$7*parameters!L30/1000</f>
-        <v>15415544.808898274</v>
+        <v>8535055.3588617258</v>
       </c>
       <c r="R29" s="24">
         <f t="shared" si="4"/>
-        <v>33100262.732829716</v>
+        <v>18326473.590118941</v>
       </c>
       <c r="S29" s="5"/>
     </row>
@@ -10617,23 +10617,23 @@
       </c>
       <c r="N30" s="22">
         <f>E30*parameters!K31/1000</f>
-        <v>21691729.156667128</v>
+        <v>11705190.436930636</v>
       </c>
       <c r="O30" s="22">
         <f>parameters!$G$7*(1-parameters!$I31)*parameters!L31/1000</f>
-        <v>10431101.487151215</v>
+        <v>5628782.6798965689</v>
       </c>
       <c r="P30" s="22">
         <f>(G30+F30)*parameters!$C$7*parameters!L31/1000</f>
-        <v>8457340.7706660312</v>
+        <v>4563711.0622062506</v>
       </c>
       <c r="Q30" s="22">
         <f>E30*parameters!$E$7*parameters!$D$7*parameters!L31/1000</f>
-        <v>16816957.928588141</v>
+        <v>9074688.961044522</v>
       </c>
       <c r="R30" s="24">
         <f t="shared" si="4"/>
-        <v>35705400.186405391</v>
+        <v>19267182.703147344</v>
       </c>
       <c r="S30" s="5"/>
     </row>
@@ -10680,23 +10680,23 @@
       </c>
       <c r="N31" s="26">
         <f>E31*parameters!K32/1000</f>
-        <v>22595551.223760899</v>
+        <v>11883492.527429283</v>
       </c>
       <c r="O31" s="22">
         <f>parameters!$G$7*(1-parameters!$I32)*parameters!L32/1000</f>
-        <v>10837508.038598666</v>
+        <v>5699681.5221401863</v>
       </c>
       <c r="P31" s="22">
         <f>(G31+F31)*parameters!$C$7*parameters!L32/1000</f>
-        <v>8783494.9091692772</v>
+        <v>4619431.2802630132</v>
       </c>
       <c r="Q31" s="22">
         <f>E31*parameters!$E$7*parameters!$D$7*parameters!L32/1000</f>
-        <v>17517664.523598056</v>
+        <v>9212921.3137001656</v>
       </c>
       <c r="R31" s="27">
         <f t="shared" si="4"/>
-        <v>37138667.471366003</v>
+        <v>19532034.116103366</v>
       </c>
       <c r="S31" s="5"/>
     </row>
@@ -14103,10 +14103,10 @@
       <c r="J7" s="35">
         <v>396</v>
       </c>
-      <c r="K7" s="37">
+      <c r="K7">
         <v>90.716669999999993</v>
       </c>
-      <c r="L7" s="37">
+      <c r="L7">
         <v>0.16879865361077112</v>
       </c>
       <c r="N7" s="35">
@@ -14150,11 +14150,11 @@
       <c r="J8" s="35">
         <v>396</v>
       </c>
-      <c r="K8" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L8" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K8">
+        <v>86.596786296943222</v>
+      </c>
+      <c r="L8">
+        <v>0.1611326885559588</v>
       </c>
       <c r="N8" s="35">
         <v>396</v>
@@ -14197,11 +14197,11 @@
       <c r="J9" s="35">
         <v>396</v>
       </c>
-      <c r="K9" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L9" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K9">
+        <v>83.506873519650654</v>
+      </c>
+      <c r="L9">
+        <v>0.15538321476484959</v>
       </c>
       <c r="N9" s="35">
         <v>396</v>
@@ -14244,11 +14244,11 @@
       <c r="J10" s="35">
         <v>396</v>
       </c>
-      <c r="K10" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L10" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K10">
+        <v>80.813103406113541</v>
+      </c>
+      <c r="L10">
+        <v>0.15037085299824154</v>
       </c>
       <c r="N10" s="35">
         <v>396</v>
@@ -14291,11 +14291,11 @@
       <c r="J11" s="35">
         <v>396</v>
       </c>
-      <c r="K11" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L11" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K11">
+        <v>78.67393302183406</v>
+      </c>
+      <c r="L11">
+        <v>0.14639044806593515</v>
       </c>
       <c r="N11" s="35">
         <v>396</v>
@@ -14338,11 +14338,11 @@
       <c r="J12" s="35">
         <v>396</v>
       </c>
-      <c r="K12" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L12" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K12">
+        <v>76.772448235807872</v>
+      </c>
+      <c r="L12">
+        <v>0.14285231034832949</v>
       </c>
       <c r="N12" s="35">
         <v>396</v>
@@ -14385,11 +14385,11 @@
       <c r="J13" s="35">
         <v>396</v>
       </c>
-      <c r="K13" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L13" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K13">
+        <v>75.029420515283846</v>
+      </c>
+      <c r="L13">
+        <v>0.13960901744052426</v>
       </c>
       <c r="N13" s="35">
         <v>396</v>
@@ -14432,11 +14432,11 @@
       <c r="J14" s="35">
         <v>396</v>
       </c>
-      <c r="K14" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L14" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K14">
+        <v>73.444849860262011</v>
+      </c>
+      <c r="L14">
+        <v>0.13666056934251952</v>
       </c>
       <c r="N14" s="35">
         <v>396</v>
@@ -14479,11 +14479,11 @@
       <c r="J15" s="35">
         <v>396</v>
       </c>
-      <c r="K15" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L15" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K15">
+        <v>72.09796480349344</v>
+      </c>
+      <c r="L15">
+        <v>0.13415438845921548</v>
       </c>
       <c r="N15" s="35">
         <v>396</v>
@@ -14526,11 +14526,11 @@
       <c r="J16" s="35">
         <v>396</v>
       </c>
-      <c r="K16" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L16" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K16">
+        <v>70.751079746724884</v>
+      </c>
+      <c r="L16">
+        <v>0.13164820757591147</v>
       </c>
       <c r="N16" s="35">
         <v>396</v>
@@ -14573,11 +14573,11 @@
       <c r="J17" s="35">
         <v>396</v>
       </c>
-      <c r="K17" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L17" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K17">
+        <v>69.562651755458504</v>
+      </c>
+      <c r="L17">
+        <v>0.12943687150240793</v>
       </c>
       <c r="N17" s="35">
         <v>396</v>
@@ -14620,11 +14620,11 @@
       <c r="J18" s="35">
         <v>396</v>
       </c>
-      <c r="K18" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L18" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K18">
+        <v>68.374223764192124</v>
+      </c>
+      <c r="L18">
+        <v>0.12722553542890438</v>
       </c>
       <c r="N18" s="35">
         <v>396</v>
@@ -14667,11 +14667,11 @@
       <c r="J19" s="35">
         <v>396</v>
       </c>
-      <c r="K19" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L19" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K19">
+        <v>66.6391202803743</v>
+      </c>
+      <c r="L19">
+        <v>0.12399698733577214</v>
       </c>
       <c r="N19" s="35">
         <v>396</v>
@@ -14714,11 +14714,11 @@
       <c r="J20" s="35">
         <v>396</v>
       </c>
-      <c r="K20" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L20" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K20">
+        <v>64.948047776856001</v>
+      </c>
+      <c r="L20">
+        <v>0.12085036872915789</v>
       </c>
       <c r="N20" s="35">
         <v>396</v>
@@ -14761,11 +14761,11 @@
       <c r="J21" s="35">
         <v>396</v>
       </c>
-      <c r="K21" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L21" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K21">
+        <v>63.299888898249371</v>
+      </c>
+      <c r="L21">
+        <v>0.11778360051946238</v>
       </c>
       <c r="N21" s="35">
         <v>396</v>
@@ -14808,11 +14808,11 @@
       <c r="J22" s="35">
         <v>396</v>
       </c>
-      <c r="K22" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L22" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K22">
+        <v>61.693554643817173</v>
+      </c>
+      <c r="L22">
+        <v>0.11479465637725547</v>
       </c>
       <c r="N22" s="35">
         <v>396</v>
@@ -14855,11 +14855,11 @@
       <c r="J23" s="35">
         <v>396</v>
       </c>
-      <c r="K23" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L23" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K23">
+        <v>60.127983647928914</v>
+      </c>
+      <c r="L23">
+        <v>0.11188156139440379</v>
       </c>
       <c r="N23" s="35">
         <v>396</v>
@@ -14902,11 +14902,11 @@
       <c r="J24" s="35">
         <v>396</v>
       </c>
-      <c r="K24" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L24" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K24">
+        <v>58.602141478776574</v>
+      </c>
+      <c r="L24">
+        <v>0.10904239077917448</v>
       </c>
       <c r="N24" s="35">
         <v>396</v>
@@ -14949,11 +14949,11 @@
       <c r="J25" s="35">
         <v>396</v>
       </c>
-      <c r="K25" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L25" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K25">
+        <v>57.115019954886435</v>
+      </c>
+      <c r="L25">
+        <v>0.10627526858445267</v>
       </c>
       <c r="N25" s="35">
         <v>396</v>
@@ -14996,11 +14996,11 @@
       <c r="J26" s="35">
         <v>396</v>
       </c>
-      <c r="K26" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L26" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K26">
+        <v>55.665636478975621</v>
+      </c>
+      <c r="L26">
+        <v>0.10357836646823253</v>
       </c>
       <c r="N26" s="35">
         <v>396</v>
@@ -15043,11 +15043,11 @@
       <c r="J27" s="35">
         <v>396</v>
       </c>
-      <c r="K27" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L27" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K27">
+        <v>54.253033388712979</v>
+      </c>
+      <c r="L27">
+        <v>0.10094990248556265</v>
       </c>
       <c r="N27" s="35">
         <v>396</v>
@@ -15090,11 +15090,11 @@
       <c r="J28" s="35">
         <v>396</v>
       </c>
-      <c r="K28" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L28" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K28">
+        <v>52.876277323955435</v>
+      </c>
+      <c r="L28">
+        <v>9.8388139911147851E-2</v>
       </c>
       <c r="N28" s="35">
         <v>396</v>
@@ -15137,11 +15137,11 @@
       <c r="J29" s="35">
         <v>396</v>
       </c>
-      <c r="K29" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L29" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K29">
+        <v>51.534458610041781</v>
+      </c>
+      <c r="L29">
+        <v>9.5891386091829289E-2</v>
       </c>
       <c r="N29" s="35">
         <v>396</v>
@@ -15184,11 +15184,11 @@
       <c r="J30" s="35">
         <v>396</v>
       </c>
-      <c r="K30" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L30" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K30">
+        <v>50.226690656736288</v>
+      </c>
+      <c r="L30">
+        <v>9.3457991328184623E-2</v>
       </c>
       <c r="N30" s="35">
         <v>396</v>
@@ -15231,11 +15231,11 @@
       <c r="J31" s="35">
         <v>396</v>
       </c>
-      <c r="K31" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L31" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K31">
+        <v>48.95210937242512</v>
+      </c>
+      <c r="L31">
+        <v>9.1086347784509428E-2</v>
       </c>
       <c r="N31" s="35">
         <v>396</v>
@@ -15278,11 +15278,11 @@
       <c r="J32" s="35">
         <v>396</v>
       </c>
-      <c r="K32" s="37">
-        <v>90.716669999999993</v>
-      </c>
-      <c r="L32" s="37">
-        <v>0.16879865361077112</v>
+      <c r="K32">
+        <v>47.709872593178375</v>
+      </c>
+      <c r="L32">
+        <v>8.8774888426459461E-2</v>
       </c>
       <c r="N32" s="35">
         <v>396</v>

--- a/data/Data_v11.xlsx
+++ b/data/Data_v11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/younglee/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD185A2-2DF1-6A4A-A9EF-290895718D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753761B3-37B3-4D47-813D-DEB0013065C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12640" yWindow="760" windowWidth="16760" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="760" windowWidth="24900" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -3017,103 +3017,103 @@
       </c>
       <c r="C3" s="3">
         <f>VLOOKUP(C1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>2264619.850394343</v>
+        <v>2529788.1933461181</v>
       </c>
       <c r="D3" s="3">
         <f>VLOOKUP(D1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>3478501.5186917325</v>
+        <v>4029587.5864846222</v>
       </c>
       <c r="E3" s="3">
         <f>VLOOKUP(E1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>3366291.7922823224</v>
+        <v>4253453.5635115458</v>
       </c>
       <c r="F3" s="3">
         <f>VLOOKUP(F1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>3764382.0574718602</v>
+        <v>5142933.9922183435</v>
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP(G1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>11243465.644637324</v>
+        <v>16528453.614901222</v>
       </c>
       <c r="H3" s="3">
         <f>VLOOKUP(H1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>10988196.042798292</v>
+        <v>16528453.614901222</v>
       </c>
       <c r="I3" s="3">
         <f>VLOOKUP(I1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>11192567.646229263</v>
+        <v>18018107.885961488</v>
       </c>
       <c r="J3" s="3">
         <f>VLOOKUP(J1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>16107662.589478489</v>
+        <v>27615663.103755601</v>
       </c>
       <c r="K3" s="3">
         <f>VLOOKUP(K1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>15806750.211433291</v>
+        <v>28816344.108266711</v>
       </c>
       <c r="L3" s="3">
         <f>VLOOKUP(L1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>21153919.357160635</v>
+        <v>40857599.367980525</v>
       </c>
       <c r="M3" s="3">
         <f>VLOOKUP(M1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>24828138.113987666</v>
+        <v>48787647.130520463</v>
       </c>
       <c r="N3" s="3">
         <f>VLOOKUP(N1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>27635499.279251926</v>
+        <v>55718086.126595974</v>
       </c>
       <c r="O3" s="3">
         <f>VLOOKUP(O1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>26934205.0131284</v>
+        <v>55718086.126595974</v>
       </c>
       <c r="P3" s="3">
         <f>VLOOKUP(P1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>26250707.192175917</v>
+        <v>55718086.126595974</v>
       </c>
       <c r="Q3" s="3">
         <f>VLOOKUP(Q1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>28378722.00031393</v>
+        <v>61803229.557679728</v>
       </c>
       <c r="R3" s="3">
         <f>VLOOKUP(R1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>27658567.288519904</v>
+        <v>61803229.557679728</v>
       </c>
       <c r="S3" s="3">
         <f>VLOOKUP(S1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>29886453.793272253</v>
+        <v>68520264.412113696</v>
       </c>
       <c r="T3" s="3">
         <f>VLOOKUP(T1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>29128038.015500385</v>
+        <v>68520264.412113696</v>
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>31035399.99356623</v>
+        <v>74908016.63464345</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>30247827.898616642</v>
+        <v>74908016.63464345</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>31621020.878267676</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="X3" s="3">
         <f>VLOOKUP(X1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>30818587.732160185</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="Y3" s="3">
         <f>VLOOKUP(Y1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>30036517.589399442</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="Z3" s="3">
         <f>VLOOKUP(Z1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>29274293.706743591</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="AA3" s="3">
         <f>VLOOKUP(AA1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>28531412.454123393</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3141,87 +3141,87 @@
       </c>
       <c r="G4" s="3">
         <f>(VLOOKUP(G1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(G1,h2portion!$C$1:$AB$5,3)/HLOOKUP(G1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1348629.5753143742</v>
+        <v>1517752.7613716819</v>
       </c>
       <c r="H4" s="3">
         <f>(VLOOKUP(H1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(H1,h2portion!$C$1:$AB$5,3)/HLOOKUP(H1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1074143.4229514475</v>
+        <v>1191235.1153780667</v>
       </c>
       <c r="I4" s="3">
         <f>(VLOOKUP(I1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(I1,h2portion!$C$1:$AB$5,3)/HLOOKUP(I1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1471856.4547232741</v>
+        <v>1618921.7613047776</v>
       </c>
       <c r="J4" s="3">
         <f>(VLOOKUP(J1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,3)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2426591.6015349999</v>
+        <v>2655807.1561525469</v>
       </c>
       <c r="K4" s="3">
         <f>(VLOOKUP(K1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,3)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2381259.6705173133</v>
+        <v>2639820.144398876</v>
       </c>
       <c r="L4" s="3">
         <f>(VLOOKUP(L1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,3)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3540309.2202619775</v>
+        <v>3941302.572784279</v>
       </c>
       <c r="M4" s="3">
         <f>(VLOOKUP(M1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,3)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4253411.4145898465</v>
+        <v>4752159.2680624407</v>
       </c>
       <c r="N4" s="3">
         <f>(VLOOKUP(N1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,3)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4804586.1341937333</v>
+        <v>5157451.7191206571</v>
       </c>
       <c r="O4" s="3">
         <f>(VLOOKUP(O1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,3)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4682662.203203409</v>
+        <v>4934547.4144848101</v>
       </c>
       <c r="P4" s="3">
         <f>(VLOOKUP(P1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,3)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4563832.2837539194</v>
+        <v>4721856.5950946612</v>
       </c>
       <c r="Q4" s="3">
         <f>(VLOOKUP(Q1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4983713.397694584</v>
+        <v>5063669.1845153505</v>
       </c>
       <c r="R4" s="3">
         <f>(VLOOKUP(R1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,3)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4485879.4191951826</v>
+        <v>4476331.1327334335</v>
       </c>
       <c r="S4" s="3">
         <f>(VLOOKUP(S1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,3)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4890749.16877646</v>
+        <v>4793899.8936988441</v>
       </c>
       <c r="T4" s="3">
         <f>(VLOOKUP(T1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,3)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4766638.715245178</v>
+        <v>4590125.846853625</v>
       </c>
       <c r="U4" s="3">
         <f>(VLOOKUP(U1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,3)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5114248.8891176973</v>
+        <v>4838720.5388868488</v>
       </c>
       <c r="V4" s="3">
         <f>(VLOOKUP(V1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,3)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4984466.7786074094</v>
+        <v>4634299.9214636618</v>
       </c>
       <c r="W4" s="3">
         <f>(VLOOKUP(W1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,3)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5236960.9510801807</v>
+        <v>4785369.2975770747</v>
       </c>
       <c r="X4" s="3">
         <f>(VLOOKUP(X1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,3)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5104064.8289658725</v>
+        <v>4583158.6540500242</v>
       </c>
       <c r="Y4" s="3">
         <f>(VLOOKUP(Y1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4974541.1550019328</v>
+        <v>4390027.1710592611</v>
       </c>
       <c r="Z4" s="3">
         <f>(VLOOKUP(Z1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4848304.3480115291</v>
+        <v>4205148.8401083043</v>
       </c>
       <c r="AA4" s="3">
         <f>(VLOOKUP(AA1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,3)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4725270.9985748157</v>
+        <v>4028524.6516150129</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3249,87 +3249,87 @@
       </c>
       <c r="G5" s="3">
         <f>(VLOOKUP(G1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(G1,h2portion!$C$1:$AB$5,4)/HLOOKUP(G1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1452370.3118770183</v>
+        <v>1634502.9737848884</v>
       </c>
       <c r="H5" s="3">
         <f>(VLOOKUP(H1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(H1,h2portion!$C$1:$AB$5,4)/HLOOKUP(H1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1361414.3383919511</v>
+        <v>1509821.2508861544</v>
       </c>
       <c r="I5" s="3">
         <f>(VLOOKUP(I1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(I1,h2portion!$C$1:$AB$5,4)/HLOOKUP(I1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1865492.4833120569</v>
+        <v>2051889.20909559</v>
       </c>
       <c r="J5" s="3">
         <f>(VLOOKUP(J1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,4)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3075563.7740385467</v>
+        <v>3366081.1630305536</v>
       </c>
       <c r="K5" s="3">
         <f>(VLOOKUP(K1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,4)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3018108.1870510136</v>
+        <v>3345818.5551102036</v>
       </c>
       <c r="L5" s="3">
         <f>(VLOOKUP(L1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,4)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>4487136.1047506472</v>
+        <v>4995371.8655056562</v>
       </c>
       <c r="M5" s="3">
         <f>(VLOOKUP(M1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,4)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5390951.6766313175</v>
+        <v>6023085.5839396045</v>
       </c>
       <c r="N5" s="3">
         <f>(VLOOKUP(N1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,4)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>6089533.5886874069</v>
+        <v>6536770.202141297</v>
       </c>
       <c r="O5" s="3">
         <f>(VLOOKUP(O1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,4)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5935002.0947578093</v>
+        <v>6254251.9555679578</v>
       </c>
       <c r="P5" s="3">
         <f>(VLOOKUP(P1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,4)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5784392.0805718284</v>
+        <v>5984678.7077362565</v>
       </c>
       <c r="Q5" s="3">
         <f>(VLOOKUP(Q1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>6316566.9807989514</v>
+        <v>6417906.2920020148</v>
       </c>
       <c r="R5" s="3">
         <f>(VLOOKUP(R1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,4)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5104621.4080496915</v>
+        <v>5093756.1165587353</v>
       </c>
       <c r="S5" s="3">
         <f>(VLOOKUP(S1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,4)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5565335.2610214902</v>
+        <v>5455127.4652435128</v>
       </c>
       <c r="T5" s="3">
         <f>(VLOOKUP(T1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,4)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5424106.1242445139</v>
+        <v>5223246.6533161942</v>
       </c>
       <c r="U5" s="3">
         <f>(VLOOKUP(U1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,4)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5819662.528996001</v>
+        <v>5506130.2683884837</v>
       </c>
       <c r="V5" s="3">
         <f>(VLOOKUP(V1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,4)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5671979.4377256734</v>
+        <v>5273513.7037345115</v>
       </c>
       <c r="W5" s="3">
         <f>(VLOOKUP(W1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,4)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5959300.3926084824</v>
+        <v>5445420.2351739127</v>
       </c>
       <c r="X5" s="3">
         <f>(VLOOKUP(X1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,4)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5808073.770892201</v>
+        <v>5215318.4684017524</v>
       </c>
       <c r="Y5" s="3">
         <f>(VLOOKUP(Y1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5660684.7625884069</v>
+        <v>4995548.1601708839</v>
       </c>
       <c r="Z5" s="3">
         <f>(VLOOKUP(Z1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5517035.9822200155</v>
+        <v>4785169.3697784152</v>
       </c>
       <c r="AA5" s="3">
         <f>(VLOOKUP(AA1,'raw data1'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,4)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>5377032.5156196179</v>
+        <v>4584183.2242515665</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4542,103 +4542,103 @@
       </c>
       <c r="C3" s="3">
         <f>VLOOKUP(C1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>4990515.6776992008</v>
+        <v>5574863.9834423997</v>
       </c>
       <c r="D3" s="3">
         <f>VLOOKUP(D1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>4932757.1934147589</v>
+        <v>5714235.5830284599</v>
       </c>
       <c r="E3" s="3">
         <f>VLOOKUP(E1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>4890066.1398132164</v>
+        <v>6178807.581648659</v>
       </c>
       <c r="F3" s="3">
         <f>VLOOKUP(F1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>4873971.3843110297</v>
+        <v>6658865.3135561999</v>
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP(G1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>4866780.1105760103</v>
+        <v>7154408.778751079</v>
       </c>
       <c r="H3" s="3">
         <f>VLOOKUP(H1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5102197.3002760746</v>
+        <v>7674729.4172057044</v>
       </c>
       <c r="I3" s="3">
         <f>VLOOKUP(I1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>5333048.6018904131</v>
+        <v>8585290.5345012955</v>
       </c>
       <c r="J3" s="3">
         <f>VLOOKUP(J1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>6964676.9461349286</v>
+        <v>11940538.926894836</v>
       </c>
       <c r="K3" s="3">
         <f>VLOOKUP(K1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>8531689.2368856184</v>
+        <v>15553614.094379906</v>
       </c>
       <c r="L3" s="3">
         <f>VLOOKUP(L1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>10506296.549979102</v>
+        <v>20292317.845814999</v>
       </c>
       <c r="M3" s="3">
         <f>VLOOKUP(M1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>13520025.309172912</v>
+        <v>26567043.446887501</v>
       </c>
       <c r="N3" s="3">
         <f>VLOOKUP(N1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>14368937.408581555</v>
+        <v>28970335.726125002</v>
       </c>
       <c r="O3" s="3">
         <f>VLOOKUP(O1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>15353203.709059615</v>
+        <v>31760771.337546006</v>
       </c>
       <c r="P3" s="3">
         <f>VLOOKUP(P1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>16095865.684642907</v>
+        <v>34164063.6167835</v>
       </c>
       <c r="Q3" s="3">
         <f>VLOOKUP(Q1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>15509639.830210429</v>
+        <v>33776920.284600005</v>
       </c>
       <c r="R3" s="3">
         <f>VLOOKUP(R1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>15827083.348318409</v>
+        <v>35365709.843208499</v>
       </c>
       <c r="S3" s="3">
         <f>VLOOKUP(S1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>16118427.78356231</v>
+        <v>36954499.228204504</v>
       </c>
       <c r="T3" s="3">
         <f>VLOOKUP(T1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>16933376.959899783</v>
+        <v>39833766.560757995</v>
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>17696585.038355824</v>
+        <v>42713033.719698995</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>17924929.103750229</v>
+        <v>44390654.825827502</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>17622417.080334097</v>
+        <v>44777798.158011004</v>
       </c>
       <c r="X3" s="3">
         <f>VLOOKUP(X1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>17323715.369004481</v>
+        <v>45164941.490194499</v>
       </c>
       <c r="Y3" s="3">
         <f>VLOOKUP(Y1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>18326473.590118941</v>
+        <v>49023291.988387004</v>
       </c>
       <c r="Z3" s="3">
         <f>VLOOKUP(Z1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>19267182.703147344</v>
+        <v>52881642.451866999</v>
       </c>
       <c r="AA3" s="3">
         <f>VLOOKUP(AA1,'raw data2'!$A$6:$R$31,18)</f>
-        <v>19532034.116103366</v>
+        <v>55004389.367054999</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4678,75 +4678,75 @@
       </c>
       <c r="J4" s="3">
         <f>(VLOOKUP(J1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,3)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>267813.48639824911</v>
+        <v>293111.11653098412</v>
       </c>
       <c r="K4" s="3">
         <f>(VLOOKUP(K1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,3)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>525620.75462337688</v>
+        <v>582693.38432439591</v>
       </c>
       <c r="L4" s="3">
         <f>(VLOOKUP(L1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,3)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>861319.57584054209</v>
+        <v>958876.99323580193</v>
       </c>
       <c r="M4" s="3">
         <f>(VLOOKUP(M1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,3)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1269906.8233776556</v>
+        <v>1418813.9570956107</v>
       </c>
       <c r="N4" s="3">
         <f>(VLOOKUP(N1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,3)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1650241.2534834095</v>
+        <v>1771440.7343370665</v>
       </c>
       <c r="O4" s="3">
         <f>(VLOOKUP(O1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,3)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2010454.732213513</v>
+        <v>2118599.1579738981</v>
       </c>
       <c r="P4" s="3">
         <f>(VLOOKUP(P1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,3)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2351323.5370149044</v>
+        <v>2432738.9483565385</v>
       </c>
       <c r="Q4" s="3">
         <f>(VLOOKUP(Q1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2291655.0035229893</v>
+        <v>2328420.9778691838</v>
       </c>
       <c r="R4" s="3">
         <f>(VLOOKUP(R1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,3)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2234631.3207125673</v>
+        <v>2229874.8620580472</v>
       </c>
       <c r="S4" s="3">
         <f>(VLOOKUP(S1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,3)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2345456.6466643289</v>
+        <v>2299010.6384728593</v>
       </c>
       <c r="T4" s="3">
         <f>(VLOOKUP(T1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,3)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2449218.2152096475</v>
+        <v>2358521.4877440631</v>
       </c>
       <c r="U4" s="3">
         <f>(VLOOKUP(U1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,3)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2546203.1401350843</v>
+        <v>2409027.3464331361</v>
       </c>
       <c r="V4" s="3">
         <f>(VLOOKUP(V1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,3)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2481589.2301594075</v>
+        <v>2307253.5709919748</v>
       </c>
       <c r="W4" s="3">
         <f>(VLOOKUP(W1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,3)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2418614.9997900184</v>
+        <v>2210053.8978178324</v>
       </c>
       <c r="X4" s="3">
         <f>(VLOOKUP(X1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,3)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2357238.8395776157</v>
+        <v>2116665.8240627963</v>
       </c>
       <c r="Y4" s="3">
         <f>(VLOOKUP(Y1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2527162.2201877851</v>
+        <v>2230217.9169114777</v>
       </c>
       <c r="Z4" s="3">
         <f>(VLOOKUP(Z1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,3)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2686943.4512215443</v>
+        <v>2330504.9201325453</v>
       </c>
       <c r="AA4" s="3">
         <f>(VLOOKUP(AA1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,3)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2727872.9548452441</v>
+        <v>2325645.1213872028</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4786,75 +4786,75 @@
       </c>
       <c r="J5" s="3">
         <f>(VLOOKUP(J1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(J1,h2portion!$C$1:$AB$5,4)/HLOOKUP(J1,h2portion!$C$1:$AB$5,2)</f>
-        <v>339438.02345824597</v>
+        <v>371501.29885903804</v>
       </c>
       <c r="K5" s="3">
         <f>(VLOOKUP(K1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(K1,h2portion!$C$1:$AB$5,4)/HLOOKUP(K1,h2portion!$C$1:$AB$5,2)</f>
-        <v>666193.74713893118</v>
+        <v>738529.98710882734</v>
       </c>
       <c r="L5" s="3">
         <f>(VLOOKUP(L1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(L1,h2portion!$C$1:$AB$5,4)/HLOOKUP(L1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1091672.4856583616</v>
+        <v>1215320.8402639816</v>
       </c>
       <c r="M5" s="3">
         <f>(VLOOKUP(M1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(M1,h2portion!$C$1:$AB$5,4)/HLOOKUP(M1,h2portion!$C$1:$AB$5,2)</f>
-        <v>1609533.0668391217</v>
+        <v>1798264.2014351345</v>
       </c>
       <c r="N5" s="3">
         <f>(VLOOKUP(N1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(N1,h2portion!$C$1:$AB$5,4)/HLOOKUP(N1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2091584.8445312981</v>
+        <v>2245198.1400318639</v>
       </c>
       <c r="O5" s="3">
         <f>(VLOOKUP(O1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(O1,h2portion!$C$1:$AB$5,4)/HLOOKUP(O1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2548134.4861775921</v>
+        <v>2685201.2583622662</v>
       </c>
       <c r="P5" s="3">
         <f>(VLOOKUP(P1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(P1,h2portion!$C$1:$AB$5,4)/HLOOKUP(P1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2980165.8783095884</v>
+        <v>3083355.1787309614</v>
       </c>
       <c r="Q5" s="3">
         <f>(VLOOKUP(Q1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Q1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Q1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2904539.4812093703</v>
+        <v>2951138.2161365245</v>
       </c>
       <c r="R5" s="3">
         <f>(VLOOKUP(R1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(R1,h2portion!$C$1:$AB$5,4)/HLOOKUP(R1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2542856.330466025</v>
+        <v>2537443.8085488128</v>
       </c>
       <c r="S5" s="3">
         <f>(VLOOKUP(S1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(S1,h2portion!$C$1:$AB$5,4)/HLOOKUP(S1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2668967.9082732024</v>
+        <v>2616115.5541242887</v>
       </c>
       <c r="T5" s="3">
         <f>(VLOOKUP(T1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(T1,h2portion!$C$1:$AB$5,4)/HLOOKUP(T1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2787041.4173075301</v>
+        <v>2683834.7963984166</v>
       </c>
       <c r="U5" s="3">
         <f>(VLOOKUP(U1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(U1,h2portion!$C$1:$AB$5,4)/HLOOKUP(U1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2897403.573257165</v>
+        <v>2741306.9804239138</v>
       </c>
       <c r="V5" s="3">
         <f>(VLOOKUP(V1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(V1,h2portion!$C$1:$AB$5,4)/HLOOKUP(V1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2823877.3998365672</v>
+        <v>2625495.4428529372</v>
       </c>
       <c r="W5" s="3">
         <f>(VLOOKUP(W1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(W1,h2portion!$C$1:$AB$5,4)/HLOOKUP(W1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2752217.0687265731</v>
+        <v>2514888.9182064994</v>
       </c>
       <c r="X5" s="3">
         <f>(VLOOKUP(X1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(X1,h2portion!$C$1:$AB$5,4)/HLOOKUP(X1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2682375.2312434944</v>
+        <v>2408619.7308300789</v>
       </c>
       <c r="Y5" s="3">
         <f>(VLOOKUP(Y1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Y1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Y1,h2portion!$C$1:$AB$5,2)</f>
-        <v>2875736.3195240316</v>
+        <v>2537834.1813130612</v>
       </c>
       <c r="Z5" s="3">
         <f>(VLOOKUP(Z1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(Z1,h2portion!$C$1:$AB$5,4)/HLOOKUP(Z1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3057556.3410452055</v>
+        <v>2651953.8746335865</v>
       </c>
       <c r="AA5" s="3">
         <f>(VLOOKUP(AA1,'raw data2'!$A$6:$N$31,14))*HLOOKUP(AA1,h2portion!$C$1:$AB$5,4)/HLOOKUP(AA1,h2portion!$C$1:$AB$5,2)</f>
-        <v>3104131.2934445883</v>
+        <v>2646423.7588199209</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="O6" s="22">
         <f>parameters!$G$7*(1-parameters!$H7)*parameters!L7/1000</f>
-        <v>967247.59244493104</v>
+        <v>974131.53007012967</v>
       </c>
       <c r="P6" s="22">
         <f>(G6+F6)*parameters!$C$7*parameters!L7/1000</f>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="R6" s="24">
         <f t="shared" ref="R6:R31" si="2">O6+P6+Q6</f>
-        <v>967247.59244493104</v>
+        <v>974131.53007012967</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6321,11 +6321,11 @@
       </c>
       <c r="O7" s="22">
         <f>parameters!$G$7*(1-parameters!$H8)*parameters!L8/1000</f>
-        <v>1593179.9371816625</v>
+        <v>1779728.1933461181</v>
       </c>
       <c r="P7" s="22">
         <f>(G7+F7)*parameters!$C$7*parameters!L8/1000</f>
-        <v>671439.91321268037</v>
+        <v>750060</v>
       </c>
       <c r="Q7" s="22">
         <f>E7*parameters!$E$7*parameters!$D$7*parameters!L8/1000</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="R7" s="24">
         <f t="shared" si="2"/>
-        <v>2264619.850394343</v>
+        <v>2529788.1933461181</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6385,11 +6385,11 @@
       </c>
       <c r="O8" s="22">
         <f>parameters!$G$7*(1-parameters!$H9)*parameters!L9/1000</f>
-        <v>2183537.8068414764</v>
+        <v>2529467.5864846222</v>
       </c>
       <c r="P8" s="22">
         <f>(G8+F8)*parameters!$C$7*parameters!L9/1000</f>
-        <v>1294963.7118502564</v>
+        <v>1500120</v>
       </c>
       <c r="Q8" s="22">
         <f>E8*parameters!$E$7*parameters!$D$7*parameters!L9/1000</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="R8" s="24">
         <f t="shared" si="2"/>
-        <v>3478501.5186917325</v>
+        <v>4029587.5864846222</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6449,11 +6449,11 @@
       </c>
       <c r="O9" s="22">
         <f>parameters!$G$7*(1-parameters!$H10)*parameters!L10/1000</f>
-        <v>2113101.1033949773</v>
+        <v>2669993.5635115458</v>
       </c>
       <c r="P9" s="22">
         <f>(G9+F9)*parameters!$C$7*parameters!L10/1000</f>
-        <v>1253190.6888873451</v>
+        <v>1583460</v>
       </c>
       <c r="Q9" s="22">
         <f>E9*parameters!$E$7*parameters!$D$7*parameters!L10/1000</f>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="R9" s="24">
         <f t="shared" si="2"/>
-        <v>3366291.7922823224</v>
+        <v>4253453.5635115458</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6513,11 +6513,11 @@
       </c>
       <c r="O10" s="22">
         <f>parameters!$G$7*(1-parameters!$H11)*parameters!L11/1000</f>
-        <v>2300360.4644540558</v>
+        <v>3142773.992218344</v>
       </c>
       <c r="P10" s="22">
         <f>(G10+F10)*parameters!$C$7*parameters!L11/1000</f>
-        <v>1464021.5930178044</v>
+        <v>2000160</v>
       </c>
       <c r="Q10" s="22">
         <f>E10*parameters!$E$7*parameters!$D$7*parameters!L11/1000</f>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="R10" s="24">
         <f t="shared" si="2"/>
-        <v>3764382.0574718602</v>
+        <v>5142933.9922183435</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6573,23 +6573,23 @@
       </c>
       <c r="N11" s="22">
         <f>E11*parameters!K12/1000</f>
-        <v>4421948.8959827079</v>
+        <v>4976477.8041129196</v>
       </c>
       <c r="O11" s="22">
         <f>parameters!$G$7*(1-parameters!$H12)*parameters!L12/1000</f>
-        <v>4100876.3646497102</v>
+        <v>6028492.1852263892</v>
       </c>
       <c r="P11" s="22">
         <f>(G11+F11)*parameters!$C$7*parameters!L12/1000</f>
-        <v>3714382.7036920725</v>
+        <v>5460327.2839854127</v>
       </c>
       <c r="Q11" s="22">
         <f>E11*parameters!$E$7*parameters!$D$7*parameters!L12/1000</f>
-        <v>3428206.5762955411</v>
+        <v>5039634.1456894213</v>
       </c>
       <c r="R11" s="24">
         <f t="shared" si="2"/>
-        <v>11243465.644637324</v>
+        <v>16528453.614901222</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6637,23 +6637,23 @@
       </c>
       <c r="N12" s="22">
         <f>E12*parameters!K13/1000</f>
-        <v>4321553.7714093123</v>
+        <v>4792643.603730361</v>
       </c>
       <c r="O12" s="22">
         <f>parameters!$G$7*(1-parameters!$H13)*parameters!L13/1000</f>
-        <v>4007770.8125111195</v>
+        <v>6028492.1852263892</v>
       </c>
       <c r="P12" s="22">
         <f>(G12+F12)*parameters!$C$7*parameters!L13/1000</f>
-        <v>3630052.0334328092</v>
+        <v>5460327.2839854127</v>
       </c>
       <c r="Q12" s="22">
         <f>E12*parameters!$E$7*parameters!$D$7*parameters!L13/1000</f>
-        <v>3350373.1968543623</v>
+        <v>5039634.1456894213</v>
       </c>
       <c r="R12" s="24">
         <f t="shared" si="2"/>
-        <v>10988196.042798292</v>
+        <v>16528453.614901222</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6701,23 +6701,23 @@
       </c>
       <c r="N13" s="22">
         <f>E13*parameters!K14/1000</f>
-        <v>5921655.0387703823</v>
+        <v>6513336.388505267</v>
       </c>
       <c r="O13" s="22">
         <f>parameters!$G$7*(1-parameters!$H14)*parameters!L14/1000</f>
-        <v>3923129.4014760382</v>
+        <v>6315563.2416657414</v>
       </c>
       <c r="P13" s="22">
         <f>(G13+F13)*parameters!$C$7*parameters!L14/1000</f>
-        <v>2678553.7221145355</v>
+        <v>4312010.5653024903</v>
       </c>
       <c r="Q13" s="22">
         <f>E13*parameters!$E$7*parameters!$D$7*parameters!L14/1000</f>
-        <v>4590884.5226386888</v>
+        <v>7390534.0789932562</v>
       </c>
       <c r="R13" s="24">
         <f t="shared" si="2"/>
-        <v>11192567.646229263</v>
+        <v>18018107.885961488</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6765,23 +6765,23 @@
       </c>
       <c r="N14" s="22">
         <f>E14*parameters!K15/1000</f>
-        <v>9762798.7689663954</v>
+        <v>10684991.581730014</v>
       </c>
       <c r="O14" s="22">
         <f>parameters!$G$7*(1-parameters!$H15)*parameters!L15/1000</f>
-        <v>5034424.7495112978</v>
+        <v>8631232.3114172257</v>
       </c>
       <c r="P14" s="22">
         <f>(G14+F14)*parameters!$C$7*parameters!L15/1000</f>
-        <v>3504427.8581904382</v>
+        <v>6008140.4465485672</v>
       </c>
       <c r="Q14" s="22">
         <f>E14*parameters!$E$7*parameters!$D$7*parameters!L15/1000</f>
-        <v>7568809.9817767544</v>
+        <v>12976290.345789809</v>
       </c>
       <c r="R14" s="24">
         <f t="shared" si="2"/>
-        <v>16107662.589478489</v>
+        <v>27615663.103755601</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6829,23 +6829,23 @@
       </c>
       <c r="N15" s="22">
         <f>E15*parameters!K16/1000</f>
-        <v>9580416.8139417488</v>
+        <v>10620671.743744316</v>
       </c>
       <c r="O15" s="22">
         <f>parameters!$G$7*(1-parameters!$H16)*parameters!L16/1000</f>
-        <v>4940375.0563885607</v>
+        <v>9006503.2814788409</v>
       </c>
       <c r="P15" s="22">
         <f>(G15+F15)*parameters!$C$7*parameters!L16/1000</f>
-        <v>3438960.5245758919</v>
+        <v>6269363.9442245914</v>
       </c>
       <c r="Q15" s="22">
         <f>E15*parameters!$E$7*parameters!$D$7*parameters!L16/1000</f>
-        <v>7427414.6304688379</v>
+        <v>13540476.882563278</v>
       </c>
       <c r="R15" s="24">
         <f t="shared" si="2"/>
-        <v>15806750.211433291</v>
+        <v>28816344.108266711</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6893,23 +6893,23 @@
       </c>
       <c r="N16" s="22">
         <f>E16*parameters!K17/1000</f>
-        <v>14243569.653612144</v>
+        <v>15856868.490504192</v>
       </c>
       <c r="O16" s="22">
         <f>parameters!$G$7*(1-parameters!$H17)*parameters!L17/1000</f>
-        <v>5661414.8161024535</v>
+        <v>10934702.66700075</v>
       </c>
       <c r="P16" s="22">
         <f>(G16+F16)*parameters!$C$7*parameters!L17/1000</f>
-        <v>4449885.0298290467</v>
+        <v>8594701.3748440761</v>
       </c>
       <c r="Q16" s="22">
         <f>E16*parameters!$E$7*parameters!$D$7*parameters!L17/1000</f>
-        <v>11042619.511229133</v>
+        <v>21328195.326135695</v>
       </c>
       <c r="R16" s="24">
         <f t="shared" si="2"/>
-        <v>21153919.357160635</v>
+        <v>40857599.367980525</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6957,23 +6957,23 @@
       </c>
       <c r="N17" s="22">
         <f>E17*parameters!K18/1000</f>
-        <v>17112562.20288473</v>
+        <v>19119152.404065166</v>
       </c>
       <c r="O17" s="22">
         <f>parameters!$G$7*(1-parameters!$H18)*parameters!L18/1000</f>
-        <v>6497928.4605944296</v>
+        <v>12768522.527117943</v>
       </c>
       <c r="P17" s="22">
         <f>(G17+F17)*parameters!$C$7*parameters!L18/1000</f>
-        <v>5063344.8249704437</v>
+        <v>9949545.1284618881</v>
       </c>
       <c r="Q17" s="22">
         <f>E17*parameters!$E$7*parameters!$D$7*parameters!L18/1000</f>
-        <v>13266864.828422792</v>
+        <v>26069579.474940632</v>
       </c>
       <c r="R17" s="24">
         <f t="shared" si="2"/>
-        <v>24828138.113987666</v>
+        <v>48787647.130520463</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7021,23 +7021,23 @@
       </c>
       <c r="N18" s="22">
         <f>E18*parameters!K19/1000</f>
-        <v>19330079.098035254</v>
+        <v>20749747.614136595</v>
       </c>
       <c r="O18" s="22">
         <f>parameters!$G$7*(1-parameters!$H19)*parameters!L19/1000</f>
-        <v>7127150.3026196016</v>
+        <v>14369603.761662271</v>
       </c>
       <c r="P18" s="22">
         <f>(G18+F18)*parameters!$C$7*parameters!L19/1000</f>
-        <v>5522308.6937152687</v>
+        <v>11133957.38954806</v>
       </c>
       <c r="Q18" s="22">
         <f>E18*parameters!$E$7*parameters!$D$7*parameters!L19/1000</f>
-        <v>14986040.282917058</v>
+        <v>30214524.975385647</v>
       </c>
       <c r="R18" s="24">
         <f t="shared" si="2"/>
-        <v>27635499.279251926</v>
+        <v>55718086.126595974</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7085,23 +7085,23 @@
       </c>
       <c r="N19" s="22">
         <f>E19*parameters!K20/1000</f>
-        <v>18839547.933818366</v>
+        <v>19852946.574555166</v>
       </c>
       <c r="O19" s="22">
         <f>parameters!$G$7*(1-parameters!$H20)*parameters!L20/1000</f>
-        <v>6946287.6523551187</v>
+        <v>14369603.761662271</v>
       </c>
       <c r="P19" s="22">
         <f>(G19+F19)*parameters!$C$7*parameters!L20/1000</f>
-        <v>5382171.4237664603</v>
+        <v>11133957.38954806</v>
       </c>
       <c r="Q19" s="22">
         <f>E19*parameters!$E$7*parameters!$D$7*parameters!L20/1000</f>
-        <v>14605745.937006822</v>
+        <v>30214524.975385647</v>
       </c>
       <c r="R19" s="24">
         <f t="shared" si="2"/>
-        <v>26934205.0131284</v>
+        <v>55718086.126595974</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7149,23 +7149,23 @@
       </c>
       <c r="N20" s="22">
         <f>E20*parameters!K21/1000</f>
-        <v>18361464.769521583</v>
+        <v>18997236.998869218</v>
       </c>
       <c r="O20" s="22">
         <f>parameters!$G$7*(1-parameters!$H21)*parameters!L21/1000</f>
-        <v>6770014.6763463719</v>
+        <v>14369603.761662271</v>
       </c>
       <c r="P20" s="22">
         <f>(G20+F20)*parameters!$C$7*parameters!L21/1000</f>
-        <v>5245590.3574849796</v>
+        <v>11133957.38954806</v>
       </c>
       <c r="Q20" s="22">
         <f>E20*parameters!$E$7*parameters!$D$7*parameters!L21/1000</f>
-        <v>14235102.158344569</v>
+        <v>30214524.975385647</v>
       </c>
       <c r="R20" s="24">
         <f t="shared" si="2"/>
-        <v>26250707.192175917</v>
+        <v>55718086.126595974</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7213,23 +7213,23 @@
       </c>
       <c r="N21" s="22">
         <f>E21*parameters!K22/1000</f>
-        <v>20050753.902352631</v>
+        <v>20372436.486538503</v>
       </c>
       <c r="O21" s="22">
         <f>parameters!$G$7*(1-parameters!$H22)*parameters!L22/1000</f>
-        <v>7244032.9228167385</v>
+        <v>15776067.352408607</v>
       </c>
       <c r="P21" s="22">
         <f>(G21+F21)*parameters!$C$7*parameters!L22/1000</f>
-        <v>5589930.8714092309</v>
+        <v>12173761.061313603</v>
       </c>
       <c r="Q21" s="22">
         <f>E21*parameters!$E$7*parameters!$D$7*parameters!L22/1000</f>
-        <v>15544758.206087964</v>
+        <v>33853401.143957518</v>
       </c>
       <c r="R21" s="24">
         <f t="shared" si="2"/>
-        <v>28378722.00031393</v>
+        <v>61803229.557679728</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7277,23 +7277,23 @@
       </c>
       <c r="N22" s="22">
         <f>E22*parameters!K23/1000</f>
-        <v>19541934.481321543</v>
+        <v>19500339.072482429</v>
       </c>
       <c r="O22" s="22">
         <f>parameters!$G$7*(1-parameters!$H23)*parameters!L23/1000</f>
-        <v>7060204.1922030114</v>
+        <v>15776067.352408607</v>
       </c>
       <c r="P22" s="22">
         <f>(G22+F22)*parameters!$C$7*parameters!L23/1000</f>
-        <v>5448077.5823286399</v>
+        <v>12173761.061313603</v>
       </c>
       <c r="Q22" s="22">
         <f>E22*parameters!$E$7*parameters!$D$7*parameters!L23/1000</f>
-        <v>15150285.513988251</v>
+        <v>33853401.143957518</v>
       </c>
       <c r="R22" s="24">
         <f t="shared" si="2"/>
-        <v>27658567.288519904</v>
+        <v>61803229.557679728</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7341,23 +7341,23 @@
       </c>
       <c r="N23" s="22">
         <f>E23*parameters!K24/1000</f>
-        <v>21305677.4134055</v>
+        <v>20883770.80128577</v>
       </c>
       <c r="O23" s="22">
         <f>parameters!$G$7*(1-parameters!$H24)*parameters!L24/1000</f>
-        <v>7558380.5133224837</v>
+        <v>17328995.767868895</v>
       </c>
       <c r="P23" s="22">
         <f>(G23+F23)*parameters!$C$7*parameters!L24/1000</f>
-        <v>5810409.8832912473</v>
+        <v>13321447.378795348</v>
       </c>
       <c r="Q23" s="22">
         <f>E23*parameters!$E$7*parameters!$D$7*parameters!L24/1000</f>
-        <v>16517663.396658521</v>
+        <v>37869821.265449449</v>
       </c>
       <c r="R23" s="24">
         <f t="shared" si="2"/>
-        <v>29886453.793272253</v>
+        <v>68520264.412113696</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7405,23 +7405,23 @@
       </c>
       <c r="N24" s="22">
         <f>E24*parameters!K25/1000</f>
-        <v>20765012.334228996</v>
+        <v>19996065.470776137</v>
       </c>
       <c r="O24" s="22">
         <f>parameters!$G$7*(1-parameters!$H25)*parameters!L25/1000</f>
-        <v>7366574.7181164427</v>
+        <v>17328995.767868895</v>
       </c>
       <c r="P24" s="22">
         <f>(G24+F24)*parameters!$C$7*parameters!L25/1000</f>
-        <v>5662961.592460514</v>
+        <v>13321447.378795348</v>
       </c>
       <c r="Q24" s="22">
         <f>E24*parameters!$E$7*parameters!$D$7*parameters!L25/1000</f>
-        <v>16098501.704923429</v>
+        <v>37869821.265449449</v>
       </c>
       <c r="R24" s="24">
         <f t="shared" si="2"/>
-        <v>29128038.015500385</v>
+        <v>68520264.412113696</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7469,23 +7469,23 @@
       </c>
       <c r="N25" s="22">
         <f>E25*parameters!K26/1000</f>
-        <v>22279314.126156405</v>
+        <v>21079023.956759952</v>
       </c>
       <c r="O25" s="22">
         <f>parameters!$G$7*(1-parameters!$H26)*parameters!L26/1000</f>
-        <v>7791447.3785817642</v>
+        <v>18805682.219779458</v>
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
-        <v>5971457.3873638483</v>
+        <v>14412897.188321883</v>
       </c>
       <c r="Q25" s="22">
         <f>E25*parameters!$E$7*parameters!$D$7*parameters!L26/1000</f>
-        <v>17272495.227620617</v>
+        <v>41689437.226542108</v>
       </c>
       <c r="R25" s="24">
         <f t="shared" si="2"/>
-        <v>31035399.99356623</v>
+        <v>74908016.63464345</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7533,23 +7533,23 @@
       </c>
       <c r="N26" s="22">
         <f>E26*parameters!K27/1000</f>
-        <v>21713941.483818486</v>
+        <v>20188501.956721008</v>
       </c>
       <c r="O26" s="22">
         <f>parameters!$G$7*(1-parameters!$H27)*parameters!L27/1000</f>
-        <v>7593727.1450448623</v>
+        <v>18805682.219779458</v>
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
-        <v>5819922.2627821369</v>
+        <v>14412897.188321883</v>
       </c>
       <c r="Q26" s="22">
         <f>E26*parameters!$E$7*parameters!$D$7*parameters!L27/1000</f>
-        <v>16834178.490789644</v>
+        <v>41689437.226542108</v>
       </c>
       <c r="R26" s="24">
         <f t="shared" si="2"/>
-        <v>30247827.898616642</v>
+        <v>74908016.63464345</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7597,23 +7597,23 @@
       </c>
       <c r="N27" s="22">
         <f>E27*parameters!K28/1000</f>
-        <v>22813887.361602169</v>
+        <v>20846608.779100131</v>
       </c>
       <c r="O27" s="22">
         <f>parameters!$G$7*(1-parameters!$H28)*parameters!L28/1000</f>
-        <v>7896110.5019278638</v>
+        <v>20063674.618350003</v>
       </c>
       <c r="P27" s="22">
         <f>(G27+F27)*parameters!$C$7*parameters!L28/1000</f>
-        <v>6037976.2837807843</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q27" s="22">
         <f>E27*parameters!$E$7*parameters!$D$7*parameters!L28/1000</f>
-        <v>17686934.092559028</v>
+        <v>44941733.090318888</v>
       </c>
       <c r="R27" s="24">
         <f t="shared" si="2"/>
-        <v>31621020.878267676</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7661,23 +7661,23 @@
       </c>
       <c r="N28" s="22">
         <f>E28*parameters!K29/1000</f>
-        <v>22234949.082506504</v>
+        <v>19965714.136608727</v>
       </c>
       <c r="O28" s="22">
         <f>parameters!$G$7*(1-parameters!$H29)*parameters!L29/1000</f>
-        <v>7695734.2769961432</v>
+        <v>20063674.618350003</v>
       </c>
       <c r="P28" s="22">
         <f>(G28+F28)*parameters!$C$7*parameters!L29/1000</f>
-        <v>5884753.1375652067</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q28" s="22">
         <f>E28*parameters!$E$7*parameters!$D$7*parameters!L29/1000</f>
-        <v>17238100.317598835</v>
+        <v>44941733.090318888</v>
       </c>
       <c r="R28" s="24">
         <f t="shared" si="2"/>
-        <v>30818587.732160185</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7725,23 +7725,23 @@
       </c>
       <c r="N29" s="22">
         <f>E29*parameters!K30/1000</f>
-        <v>21670702.272939455</v>
+        <v>19124371.239442069</v>
       </c>
       <c r="O29" s="22">
         <f>parameters!$G$7*(1-parameters!$H30)*parameters!L30/1000</f>
-        <v>7500442.9139730902</v>
+        <v>20063674.618350003</v>
       </c>
       <c r="P29" s="22">
         <f>(G29+F29)*parameters!$C$7*parameters!L30/1000</f>
-        <v>5735418.2697119107</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q29" s="22">
         <f>E29*parameters!$E$7*parameters!$D$7*parameters!L30/1000</f>
-        <v>16800656.405714441</v>
+        <v>44941733.090318888</v>
       </c>
       <c r="R29" s="24">
         <f t="shared" si="2"/>
-        <v>30036517.589399442</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7789,23 +7789,23 @@
       </c>
       <c r="N30" s="22">
         <f>E30*parameters!K31/1000</f>
-        <v>21120774.113751374</v>
+        <v>18318981.72874767</v>
       </c>
       <c r="O30" s="22">
         <f>parameters!$G$7*(1-parameters!$H31)*parameters!L31/1000</f>
-        <v>7310107.3764890507</v>
+        <v>20063674.618350003</v>
       </c>
       <c r="P30" s="22">
         <f>(G30+F30)*parameters!$C$7*parameters!L31/1000</f>
-        <v>5589873.0090410151</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q30" s="22">
         <f>E30*parameters!$E$7*parameters!$D$7*parameters!L31/1000</f>
-        <v>16374313.321213527</v>
+        <v>44941733.090318888</v>
       </c>
       <c r="R30" s="24">
         <f t="shared" si="2"/>
-        <v>29274293.706743591</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7853,23 +7853,23 @@
       </c>
       <c r="N31" s="26">
         <f>E31*parameters!K32/1000</f>
-        <v>20584801.246665001</v>
+        <v>17549549.919104483</v>
       </c>
       <c r="O31" s="22">
         <f>parameters!$G$7*(1-parameters!$H32)*parameters!L32/1000</f>
-        <v>7124601.9026752319</v>
+        <v>20063674.618350003</v>
       </c>
       <c r="P31" s="22">
         <f>(G31+F31)*parameters!$C$7*parameters!L32/1000</f>
-        <v>5448021.1883090371</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q31" s="22">
         <f>E31*parameters!$E$7*parameters!$D$7*parameters!L32/1000</f>
-        <v>15958789.363139125</v>
+        <v>44941733.090318896</v>
       </c>
       <c r="R31" s="27">
         <f t="shared" si="2"/>
-        <v>28531412.454123393</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9109,11 +9109,11 @@
       </c>
       <c r="O6" s="22">
         <f>parameters!$G$7*(1-parameters!$I7)*parameters!L7/1000</f>
-        <v>1806251.3397664437</v>
+        <v>1819106.4987303999</v>
       </c>
       <c r="P6" s="22">
         <f>(G6+F6)*parameters!$C$7*parameters!L7/1000</f>
-        <v>1679043.2323382129</v>
+        <v>1690993.0464000001</v>
       </c>
       <c r="Q6" s="22">
         <f>E6*parameters!$E$7*parameters!$D$7*parameters!L7/1000</f>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="R6" s="24">
         <f>O6+P6+Q6</f>
-        <v>3485294.5721046566</v>
+        <v>3510099.5451304</v>
       </c>
       <c r="S6" s="5"/>
     </row>
@@ -9172,11 +9172,11 @@
       </c>
       <c r="O7" s="22">
         <f>parameters!$G$7*(1-parameters!$I8)*parameters!L8/1000</f>
-        <v>2586331.0668533486</v>
+        <v>2889169.1450423994</v>
       </c>
       <c r="P7" s="22">
         <f>(G7+F7)*parameters!$C$7*parameters!L8/1000</f>
-        <v>2404184.6108458517</v>
+        <v>2685694.8384000002</v>
       </c>
       <c r="Q7" s="22">
         <f>E7*parameters!$E$7*parameters!$D$7*parameters!L8/1000</f>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="R7" s="24">
         <f>O7+P7+Q6</f>
-        <v>4990515.6776992008</v>
+        <v>5574863.9834423997</v>
       </c>
       <c r="S7" s="5"/>
     </row>
@@ -9235,11 +9235,11 @@
       </c>
       <c r="O8" s="22">
         <f>parameters!$G$7*(1-parameters!$I9)*parameters!L9/1000</f>
-        <v>2556397.7750000143</v>
+        <v>2961398.3736684597</v>
       </c>
       <c r="P8" s="22">
         <f>(G8+F8)*parameters!$C$7*parameters!L9/1000</f>
-        <v>2376359.418414745</v>
+        <v>2752837.2093600002</v>
       </c>
       <c r="Q8" s="22">
         <f>E8*parameters!$E$7*parameters!$D$7*parameters!L9/1000</f>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="R8" s="24">
         <f t="shared" ref="R8:R31" si="4">O8+P8+Q8</f>
-        <v>4932757.1934147589</v>
+        <v>5714235.5830284599</v>
       </c>
       <c r="S8" s="5"/>
     </row>
@@ -9298,11 +9298,11 @@
       </c>
       <c r="O9" s="22">
         <f>parameters!$G$7*(1-parameters!$I10)*parameters!L10/1000</f>
-        <v>2534273.1679779845</v>
+        <v>3202162.4690886596</v>
       </c>
       <c r="P9" s="22">
         <f>(G9+F9)*parameters!$C$7*parameters!L10/1000</f>
-        <v>2355792.9718352314</v>
+        <v>2976645.1125599998</v>
       </c>
       <c r="Q9" s="22">
         <f>E9*parameters!$E$7*parameters!$D$7*parameters!L10/1000</f>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="R9" s="24">
         <f t="shared" si="4"/>
-        <v>4890066.1398132164</v>
+        <v>6178807.581648659</v>
       </c>
       <c r="S9" s="5"/>
     </row>
@@ -9361,11 +9361,11 @@
       </c>
       <c r="O10" s="22">
         <f>parameters!$G$7*(1-parameters!$I11)*parameters!L11/1000</f>
-        <v>2525932.0728172725</v>
+        <v>3450952.0343561997</v>
       </c>
       <c r="P10" s="22">
         <f>(G10+F10)*parameters!$C$7*parameters!L11/1000</f>
-        <v>2348039.3114937567</v>
+        <v>3207913.2792000002</v>
       </c>
       <c r="Q10" s="22">
         <f>E10*parameters!$E$7*parameters!$D$7*parameters!L11/1000</f>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="R10" s="24">
         <f t="shared" si="4"/>
-        <v>4873971.3843110297</v>
+        <v>6658865.3135561999</v>
       </c>
       <c r="S10" s="5"/>
     </row>
@@ -9424,11 +9424,11 @@
       </c>
       <c r="O11" s="22">
         <f>parameters!$G$7*(1-parameters!$I12)*parameters!L12/1000</f>
-        <v>2522205.2005114229</v>
+        <v>3707767.0694710799</v>
       </c>
       <c r="P11" s="22">
         <f>(G11+F11)*parameters!$C$7*parameters!L12/1000</f>
-        <v>2344574.9100645874</v>
+        <v>3446641.7092799996</v>
       </c>
       <c r="Q11" s="22">
         <f>E11*parameters!$E$7*parameters!$D$7*parameters!L12/1000</f>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="R11" s="24">
         <f t="shared" si="4"/>
-        <v>4866780.1105760103</v>
+        <v>7154408.778751079</v>
       </c>
       <c r="S11" s="5"/>
     </row>
@@ -9487,11 +9487,11 @@
       </c>
       <c r="O12" s="22">
         <f>parameters!$G$7*(1-parameters!$I13)*parameters!L13/1000</f>
-        <v>2644209.985330232</v>
+        <v>3977422.8563417038</v>
       </c>
       <c r="P12" s="22">
         <f>(G12+F12)*parameters!$C$7*parameters!L13/1000</f>
-        <v>2457987.3149458426</v>
+        <v>3697306.5608640001</v>
       </c>
       <c r="Q12" s="22">
         <f>E12*parameters!$E$7*parameters!$D$7*parameters!L13/1000</f>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="R12" s="24">
         <f t="shared" si="4"/>
-        <v>5102197.3002760746</v>
+        <v>7674729.4172057044</v>
       </c>
       <c r="S12" s="5"/>
     </row>
@@ -9550,11 +9550,11 @@
       </c>
       <c r="O13" s="22">
         <f>parameters!$G$7*(1-parameters!$I14)*parameters!L14/1000</f>
-        <v>2763848.5020183437</v>
+        <v>4449320.4833652964</v>
       </c>
       <c r="P13" s="22">
         <f>(G13+F13)*parameters!$C$7*parameters!L14/1000</f>
-        <v>2569200.0998720699</v>
+        <v>4135970.0511359996</v>
       </c>
       <c r="Q13" s="22">
         <f>E13*parameters!$E$7*parameters!$D$7*parameters!L14/1000</f>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="R13" s="24">
         <f t="shared" si="4"/>
-        <v>5333048.6018904131</v>
+        <v>8585290.5345012955</v>
       </c>
       <c r="S13" s="5"/>
     </row>
@@ -9609,23 +9609,23 @@
       </c>
       <c r="N14" s="22">
         <f>E14*parameters!K15/1000</f>
-        <v>1077482.1662069091</v>
+        <v>1179261.0037176802</v>
       </c>
       <c r="O14" s="22">
         <f>parameters!$G$7*(1-parameters!$I15)*parameters!L15/1000</f>
-        <v>3208422.9584139576</v>
+        <v>5500657.0333668357</v>
       </c>
       <c r="P14" s="22">
         <f>(G14+F14)*parameters!$C$7*parameters!L15/1000</f>
-        <v>2920913.8390848129</v>
+        <v>5007739.1481959997</v>
       </c>
       <c r="Q14" s="22">
         <f>E14*parameters!$E$7*parameters!$D$7*parameters!L15/1000</f>
-        <v>835340.14863615844</v>
+        <v>1432142.7453320003</v>
       </c>
       <c r="R14" s="24">
         <f t="shared" si="4"/>
-        <v>6964676.9461349286</v>
+        <v>11940538.926894836</v>
       </c>
       <c r="S14" s="5"/>
     </row>
@@ -9672,23 +9672,23 @@
       </c>
       <c r="N15" s="22">
         <f>E15*parameters!K16/1000</f>
-        <v>2114706.7569731208</v>
+        <v>2344324.5462353602</v>
       </c>
       <c r="O15" s="22">
         <f>parameters!$G$7*(1-parameters!$I16)*parameters!L16/1000</f>
-        <v>3634493.198027513</v>
+        <v>6625827.9059639061</v>
       </c>
       <c r="P15" s="22">
         <f>(G15+F15)*parameters!$C$7*parameters!L16/1000</f>
-        <v>3257726.2526337323</v>
+        <v>5938966.545984</v>
       </c>
       <c r="Q15" s="22">
         <f>E15*parameters!$E$7*parameters!$D$7*parameters!L16/1000</f>
-        <v>1639469.7862243729</v>
+        <v>2988819.642432</v>
       </c>
       <c r="R15" s="24">
         <f t="shared" si="4"/>
-        <v>8531689.2368856184</v>
+        <v>15553614.094379906</v>
       </c>
       <c r="S15" s="5"/>
     </row>
@@ -9735,23 +9735,23 @@
       </c>
       <c r="N16" s="22">
         <f>E16*parameters!K17/1000</f>
-        <v>3465308.9911724133</v>
+        <v>3857807.43790218</v>
       </c>
       <c r="O16" s="22">
         <f>parameters!$G$7*(1-parameters!$I17)*parameters!L17/1000</f>
-        <v>4155166.8375063888</v>
+        <v>8025469.8473400008</v>
       </c>
       <c r="P16" s="22">
         <f>(G16+F16)*parameters!$C$7*parameters!L17/1000</f>
-        <v>3664577.8431768022</v>
+        <v>7077924.9387000008</v>
       </c>
       <c r="Q16" s="22">
         <f>E16*parameters!$E$7*parameters!$D$7*parameters!L17/1000</f>
-        <v>2686551.8692959119</v>
+        <v>5188923.0597749995</v>
       </c>
       <c r="R16" s="24">
         <f t="shared" si="4"/>
-        <v>10506296.549979102</v>
+        <v>20292317.845814999</v>
       </c>
       <c r="S16" s="5"/>
     </row>
@@ -9798,23 +9798,23 @@
       </c>
       <c r="N17" s="22">
         <f>E17*parameters!K18/1000</f>
-        <v>5109160.0103333583</v>
+        <v>5708251.5018032705</v>
       </c>
       <c r="O17" s="22">
         <f>parameters!$G$7*(1-parameters!$I18)*parameters!L18/1000</f>
-        <v>5105223.4919817951</v>
+        <v>10031837.309175001</v>
       </c>
       <c r="P17" s="22">
         <f>(G17+F17)*parameters!$C$7*parameters!L18/1000</f>
-        <v>4453820.7297155373</v>
+        <v>8751821.5480500013</v>
       </c>
       <c r="Q17" s="22">
         <f>E17*parameters!$E$7*parameters!$D$7*parameters!L18/1000</f>
-        <v>3960981.0874755788</v>
+        <v>7783384.5896624997</v>
       </c>
       <c r="R17" s="24">
         <f t="shared" si="4"/>
-        <v>13520025.309172912</v>
+        <v>26567043.446887501</v>
       </c>
       <c r="S17" s="5"/>
     </row>
@@ -9861,23 +9861,23 @@
       </c>
       <c r="N18" s="22">
         <f>E18*parameters!K19/1000</f>
-        <v>6639342.7175030187</v>
+        <v>7126959.2334956406</v>
       </c>
       <c r="O18" s="22">
         <f>parameters!$G$7*(1-parameters!$I19)*parameters!L19/1000</f>
-        <v>4975670.4151211958</v>
+        <v>10031837.309175001</v>
       </c>
       <c r="P18" s="22">
         <f>(G18+F18)*parameters!$C$7*parameters!L19/1000</f>
-        <v>4245980.3780266261</v>
+        <v>8560652.2974000014</v>
       </c>
       <c r="Q18" s="22">
         <f>E18*parameters!$E$7*parameters!$D$7*parameters!L19/1000</f>
-        <v>5147286.615433733</v>
+        <v>10377846.119549999</v>
       </c>
       <c r="R18" s="24">
         <f t="shared" si="4"/>
-        <v>14368937.408581555</v>
+        <v>28970335.726125002</v>
       </c>
       <c r="S18" s="5"/>
     </row>
@@ -9924,23 +9924,23 @@
       </c>
       <c r="N19" s="22">
         <f>E19*parameters!K20/1000</f>
-        <v>8088573.6900683194</v>
+        <v>8523666.3797554504</v>
       </c>
       <c r="O19" s="22">
         <f>parameters!$G$7*(1-parameters!$I20)*parameters!L20/1000</f>
-        <v>4946393.0504064653</v>
+        <v>10232474.055358501</v>
       </c>
       <c r="P19" s="22">
         <f>(G19+F19)*parameters!$C$7*parameters!L20/1000</f>
-        <v>4135978.0078427587</v>
+        <v>8555989.6327500008</v>
       </c>
       <c r="Q19" s="22">
         <f>E19*parameters!$E$7*parameters!$D$7*parameters!L20/1000</f>
-        <v>6270832.6508103898</v>
+        <v>12972307.6494375</v>
       </c>
       <c r="R19" s="24">
         <f t="shared" si="4"/>
-        <v>15353203.709059615</v>
+        <v>31760771.337546006</v>
       </c>
       <c r="S19" s="5"/>
     </row>
@@ -9987,23 +9987,23 @@
       </c>
       <c r="N20" s="22">
         <f>E20*parameters!K21/1000</f>
-        <v>9459976.0907808952</v>
+        <v>9787531.1178065389</v>
       </c>
       <c r="O20" s="22">
         <f>parameters!$G$7*(1-parameters!$I21)*parameters!L21/1000</f>
-        <v>4820870.5458484357</v>
+        <v>10232474.055358501</v>
       </c>
       <c r="P20" s="22">
         <f>(G20+F20)*parameters!$C$7*parameters!L21/1000</f>
-        <v>3940954.6492092926</v>
+        <v>8364820.3821</v>
       </c>
       <c r="Q20" s="22">
         <f>E20*parameters!$E$7*parameters!$D$7*parameters!L21/1000</f>
-        <v>7334040.4895851789</v>
+        <v>15566769.179324999</v>
       </c>
       <c r="R20" s="24">
         <f t="shared" si="4"/>
-        <v>16095865.684642907</v>
+        <v>34164063.6167835</v>
       </c>
       <c r="S20" s="5"/>
     </row>
@@ -10050,23 +10050,23 @@
       </c>
       <c r="N21" s="22">
         <f>E21*parameters!K22/1000</f>
-        <v>9219914.3164994679</v>
+        <v>9367833.2365434617</v>
       </c>
       <c r="O21" s="22">
         <f>parameters!$G$7*(1-parameters!$I22)*parameters!L22/1000</f>
-        <v>4606405.2669571014</v>
+        <v>10031837.309175001</v>
       </c>
       <c r="P21" s="22">
         <f>(G21+F21)*parameters!$C$7*parameters!L22/1000</f>
-        <v>3755306.8878746689</v>
+        <v>8178313.7960999999</v>
       </c>
       <c r="Q21" s="22">
         <f>E21*parameters!$E$7*parameters!$D$7*parameters!L22/1000</f>
-        <v>7147927.6753786569</v>
+        <v>15566769.179324999</v>
       </c>
       <c r="R21" s="24">
         <f t="shared" si="4"/>
-        <v>15509639.830210429</v>
+        <v>33776920.284600005</v>
       </c>
       <c r="S21" s="5"/>
     </row>
@@ -10113,23 +10113,23 @@
       </c>
       <c r="N22" s="22">
         <f>E22*parameters!K23/1000</f>
-        <v>9734773.2247133683</v>
+        <v>9714052.5600000005</v>
       </c>
       <c r="O22" s="22">
         <f>parameters!$G$7*(1-parameters!$I23)*parameters!L23/1000</f>
-        <v>4579300.6969649447</v>
+        <v>10232474.055358501</v>
       </c>
       <c r="P22" s="22">
         <f>(G22+F22)*parameters!$C$7*parameters!L23/1000</f>
-        <v>3700700.0475660339</v>
+        <v>8269235.7915000003</v>
       </c>
       <c r="Q22" s="22">
         <f>E22*parameters!$E$7*parameters!$D$7*parameters!L23/1000</f>
-        <v>7547082.6037874306</v>
+        <v>16863999.996349998</v>
       </c>
       <c r="R22" s="24">
         <f t="shared" si="4"/>
-        <v>15827083.348318409</v>
+        <v>35365709.843208499</v>
       </c>
       <c r="S22" s="5"/>
     </row>
@@ -10176,23 +10176,23 @@
       </c>
       <c r="N23" s="22">
         <f>E23*parameters!K24/1000</f>
-        <v>10217564.012480238</v>
+        <v>10015230.25265763</v>
       </c>
       <c r="O23" s="22">
         <f>parameters!$G$7*(1-parameters!$I24)*parameters!L24/1000</f>
-        <v>4550605.380256677</v>
+        <v>10433110.801542001</v>
       </c>
       <c r="P23" s="22">
         <f>(G23+F23)*parameters!$C$7*parameters!L24/1000</f>
-        <v>3646446.3392068571</v>
+        <v>8360157.7174500003</v>
       </c>
       <c r="Q23" s="22">
         <f>E23*parameters!$E$7*parameters!$D$7*parameters!L24/1000</f>
-        <v>7921376.0640987745</v>
+        <v>18161230.709212501</v>
       </c>
       <c r="R23" s="24">
         <f t="shared" si="4"/>
-        <v>16118427.78356231</v>
+        <v>36954499.228204504</v>
       </c>
       <c r="S23" s="5"/>
     </row>
@@ -10239,23 +10239,23 @@
       </c>
       <c r="N24" s="22">
         <f>E24*parameters!K25/1000</f>
-        <v>10669582.799591454</v>
+        <v>10274478.664999999</v>
       </c>
       <c r="O24" s="22">
         <f>parameters!$G$7*(1-parameters!$I25)*parameters!L25/1000</f>
-        <v>4804720.4946226655</v>
+        <v>11302536.701670501</v>
       </c>
       <c r="P24" s="22">
         <f>(G24+F24)*parameters!$C$7*parameters!L25/1000</f>
-        <v>3856843.5655126027</v>
+        <v>9072768.3328499999</v>
       </c>
       <c r="Q24" s="22">
         <f>E24*parameters!$E$7*parameters!$D$7*parameters!L25/1000</f>
-        <v>8271812.8997645164</v>
+        <v>19458461.526237499</v>
       </c>
       <c r="R24" s="24">
         <f t="shared" si="4"/>
-        <v>16933376.959899783</v>
+        <v>39833766.560757995</v>
       </c>
       <c r="S24" s="5"/>
     </row>
@@ -10302,23 +10302,23 @@
       </c>
       <c r="N25" s="22">
         <f>E25*parameters!K26/1000</f>
-        <v>11092080.346105712</v>
+        <v>10494498.44020872</v>
       </c>
       <c r="O25" s="22">
         <f>parameters!$G$7*(1-parameters!$I26)*parameters!L26/1000</f>
-        <v>5043008.0120270317</v>
+        <v>12171962.601799002</v>
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
-        <v>4054214.2381553957</v>
+        <v>9785378.878800001</v>
       </c>
       <c r="Q25" s="22">
         <f>E25*parameters!$E$7*parameters!$D$7*parameters!L26/1000</f>
-        <v>8599362.7881733961</v>
+        <v>20755692.239099998</v>
       </c>
       <c r="R25" s="24">
         <f t="shared" si="4"/>
-        <v>17696585.038355824</v>
+        <v>42713033.719698995</v>
       </c>
       <c r="S25" s="5"/>
     </row>
@@ -10365,23 +10365,23 @@
       </c>
       <c r="N26" s="22">
         <f>E26*parameters!K27/1000</f>
-        <v>10810601.358970294</v>
+        <v>10051139.119608719</v>
       </c>
       <c r="O26" s="22">
         <f>parameters!$G$7*(1-parameters!$I27)*parameters!L27/1000</f>
-        <v>5266107.5901836781</v>
+        <v>13041388.501927502</v>
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
-        <v>4277681.083336575</v>
+        <v>10593574.084800001</v>
       </c>
       <c r="Q26" s="22">
         <f>E26*parameters!$E$7*parameters!$D$7*parameters!L27/1000</f>
-        <v>8381140.4302299777</v>
+        <v>20755692.239099998</v>
       </c>
       <c r="R26" s="24">
         <f t="shared" si="4"/>
-        <v>17924929.103750229</v>
+        <v>44390654.825827502</v>
       </c>
       <c r="S26" s="5"/>
     </row>
@@ -10428,23 +10428,23 @@
       </c>
       <c r="N27" s="22">
         <f>E27*parameters!K28/1000</f>
-        <v>10536265.34391284</v>
+        <v>9627706.0606087185</v>
       </c>
       <c r="O27" s="22">
         <f>parameters!$G$7*(1-parameters!$I28)*parameters!L28/1000</f>
-        <v>5211432.9312723894</v>
+        <v>13242025.248111</v>
       </c>
       <c r="P27" s="22">
         <f>(G27+F27)*parameters!$C$7*parameters!L28/1000</f>
-        <v>4242528.3411685247</v>
+        <v>10780080.6708</v>
       </c>
       <c r="Q27" s="22">
         <f>E27*parameters!$E$7*parameters!$D$7*parameters!L28/1000</f>
-        <v>8168455.8078931849</v>
+        <v>20755692.239099998</v>
       </c>
       <c r="R27" s="24">
         <f t="shared" si="4"/>
-        <v>17622417.080334097</v>
+        <v>44777798.158011004</v>
       </c>
       <c r="S27" s="5"/>
     </row>
@@ -10491,23 +10491,23 @@
       </c>
       <c r="N28" s="22">
         <f>E28*parameters!K29/1000</f>
-        <v>10268891.03678065</v>
+        <v>9220877.555399999</v>
       </c>
       <c r="O28" s="22">
         <f>parameters!$G$7*(1-parameters!$I29)*parameters!L29/1000</f>
-        <v>5156141.9655874157</v>
+        <v>13442661.9942945</v>
       </c>
       <c r="P28" s="22">
         <f>(G28+F28)*parameters!$C$7*parameters!L29/1000</f>
-        <v>4206405.0110061755</v>
+        <v>10966587.256800001</v>
       </c>
       <c r="Q28" s="22">
         <f>E28*parameters!$E$7*parameters!$D$7*parameters!L29/1000</f>
-        <v>7961168.3924108902</v>
+        <v>20755692.239099998</v>
       </c>
       <c r="R28" s="24">
         <f t="shared" si="4"/>
-        <v>17323715.369004481</v>
+        <v>45164941.490194499</v>
       </c>
       <c r="S28" s="5"/>
     </row>
@@ -10554,23 +10554,23 @@
       </c>
       <c r="N29" s="22">
         <f>E29*parameters!K30/1000</f>
-        <v>11009131.97070311</v>
+        <v>9715547.0173500013</v>
       </c>
       <c r="O29" s="22">
         <f>parameters!$G$7*(1-parameters!$I30)*parameters!L30/1000</f>
-        <v>5400318.8980606254</v>
+        <v>14445845.725212002</v>
       </c>
       <c r="P29" s="22">
         <f>(G29+F29)*parameters!$C$7*parameters!L30/1000</f>
-        <v>4391099.3331965897</v>
+        <v>11746184.7585</v>
       </c>
       <c r="Q29" s="22">
         <f>E29*parameters!$E$7*parameters!$D$7*parameters!L30/1000</f>
-        <v>8535055.3588617258</v>
+        <v>22831261.504675001</v>
       </c>
       <c r="R29" s="24">
         <f t="shared" si="4"/>
-        <v>18326473.590118941</v>
+        <v>49023291.988387004</v>
       </c>
       <c r="S29" s="5"/>
     </row>
@@ -10617,23 +10617,23 @@
       </c>
       <c r="N30" s="22">
         <f>E30*parameters!K31/1000</f>
-        <v>11705190.436930636</v>
+        <v>10152429.479657872</v>
       </c>
       <c r="O30" s="22">
         <f>parameters!$G$7*(1-parameters!$I31)*parameters!L31/1000</f>
-        <v>5628782.6798965689</v>
+        <v>15449029.456129501</v>
       </c>
       <c r="P30" s="22">
         <f>(G30+F30)*parameters!$C$7*parameters!L31/1000</f>
-        <v>4563711.0622062506</v>
+        <v>12525782.32965</v>
       </c>
       <c r="Q30" s="22">
         <f>E30*parameters!$E$7*parameters!$D$7*parameters!L31/1000</f>
-        <v>9074688.961044522</v>
+        <v>24906830.666087497</v>
       </c>
       <c r="R30" s="24">
         <f t="shared" si="4"/>
-        <v>19267182.703147344</v>
+        <v>52881642.451866999</v>
       </c>
       <c r="S30" s="5"/>
     </row>
@@ -10680,23 +10680,23 @@
       </c>
       <c r="N31" s="26">
         <f>E31*parameters!K32/1000</f>
-        <v>11883492.527429283</v>
+        <v>10131258.63225</v>
       </c>
       <c r="O31" s="22">
         <f>parameters!$G$7*(1-parameters!$I32)*parameters!L32/1000</f>
-        <v>5699681.5221401863</v>
+        <v>16050939.694680002</v>
       </c>
       <c r="P31" s="22">
         <f>(G31+F31)*parameters!$C$7*parameters!L32/1000</f>
-        <v>4619431.2802630132</v>
+        <v>13008834.373500001</v>
       </c>
       <c r="Q31" s="22">
         <f>E31*parameters!$E$7*parameters!$D$7*parameters!L32/1000</f>
-        <v>9212921.3137001656</v>
+        <v>25944615.298875</v>
       </c>
       <c r="R31" s="27">
         <f t="shared" si="4"/>
-        <v>19532034.116103366</v>
+        <v>55004389.367054999</v>
       </c>
       <c r="S31" s="5"/>
     </row>
@@ -14103,11 +14103,11 @@
       <c r="J7" s="35">
         <v>396</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="37">
         <v>90.716669999999993</v>
       </c>
-      <c r="L7">
-        <v>0.16879865361077112</v>
+      <c r="L7" s="35">
+        <v>0.17</v>
       </c>
       <c r="N7" s="35">
         <v>396</v>
@@ -14150,11 +14150,11 @@
       <c r="J8" s="35">
         <v>396</v>
       </c>
-      <c r="K8">
-        <v>86.596786296943222</v>
-      </c>
-      <c r="L8">
-        <v>0.1611326885559588</v>
+      <c r="K8" s="37">
+        <v>89.674999999999997</v>
+      </c>
+      <c r="L8" s="35">
+        <v>0.18</v>
       </c>
       <c r="N8" s="35">
         <v>396</v>
@@ -14197,11 +14197,11 @@
       <c r="J9" s="35">
         <v>396</v>
       </c>
-      <c r="K9">
-        <v>83.506873519650654</v>
-      </c>
-      <c r="L9">
-        <v>0.15538321476484959</v>
+      <c r="K9" s="37">
+        <v>87.974999999999994</v>
+      </c>
+      <c r="L9" s="35">
+        <v>0.18</v>
       </c>
       <c r="N9" s="35">
         <v>396</v>
@@ -14244,11 +14244,11 @@
       <c r="J10" s="35">
         <v>396</v>
       </c>
-      <c r="K10">
-        <v>80.813103406113541</v>
-      </c>
-      <c r="L10">
-        <v>0.15037085299824154</v>
+      <c r="K10" s="37">
+        <v>89.741669999999999</v>
+      </c>
+      <c r="L10" s="35">
+        <v>0.19</v>
       </c>
       <c r="N10" s="35">
         <v>396</v>
@@ -14291,11 +14291,11 @@
       <c r="J11" s="35">
         <v>396</v>
       </c>
-      <c r="K11">
-        <v>78.67393302183406</v>
-      </c>
-      <c r="L11">
-        <v>0.14639044806593515</v>
+      <c r="K11" s="37">
+        <v>89.8</v>
+      </c>
+      <c r="L11" s="35">
+        <v>0.2</v>
       </c>
       <c r="N11" s="35">
         <v>396</v>
@@ -14338,11 +14338,11 @@
       <c r="J12" s="35">
         <v>396</v>
       </c>
-      <c r="K12">
-        <v>76.772448235807872</v>
-      </c>
-      <c r="L12">
-        <v>0.14285231034832949</v>
+      <c r="K12" s="37">
+        <v>86.4</v>
+      </c>
+      <c r="L12" s="35">
+        <v>0.21</v>
       </c>
       <c r="N12" s="35">
         <v>396</v>
@@ -14385,11 +14385,11 @@
       <c r="J13" s="35">
         <v>396</v>
       </c>
-      <c r="K13">
-        <v>75.029420515283846</v>
-      </c>
-      <c r="L13">
-        <v>0.13960901744052426</v>
+      <c r="K13" s="37">
+        <v>83.208330000000004</v>
+      </c>
+      <c r="L13" s="35">
+        <v>0.21</v>
       </c>
       <c r="N13" s="35">
         <v>396</v>
@@ -14432,11 +14432,11 @@
       <c r="J14" s="35">
         <v>396</v>
       </c>
-      <c r="K14">
-        <v>73.444849860262011</v>
-      </c>
-      <c r="L14">
-        <v>0.13666056934251952</v>
+      <c r="K14" s="37">
+        <v>80.783330000000007</v>
+      </c>
+      <c r="L14" s="35">
+        <v>0.22</v>
       </c>
       <c r="N14" s="35">
         <v>396</v>
@@ -14479,11 +14479,11 @@
       <c r="J15" s="35">
         <v>396</v>
       </c>
-      <c r="K15">
-        <v>72.09796480349344</v>
-      </c>
-      <c r="L15">
-        <v>0.13415438845921548</v>
+      <c r="K15" s="37">
+        <v>78.908330000000007</v>
+      </c>
+      <c r="L15" s="35">
+        <v>0.23</v>
       </c>
       <c r="N15" s="35">
         <v>396</v>
@@ -14526,11 +14526,11 @@
       <c r="J16" s="35">
         <v>396</v>
       </c>
-      <c r="K16">
-        <v>70.751079746724884</v>
-      </c>
-      <c r="L16">
-        <v>0.13164820757591147</v>
+      <c r="K16" s="37">
+        <v>78.433329999999998</v>
+      </c>
+      <c r="L16" s="35">
+        <v>0.24</v>
       </c>
       <c r="N16" s="35">
         <v>396</v>
@@ -14573,11 +14573,11 @@
       <c r="J17" s="35">
         <v>396</v>
       </c>
-      <c r="K17">
-        <v>69.562651755458504</v>
-      </c>
-      <c r="L17">
-        <v>0.12943687150240793</v>
+      <c r="K17" s="37">
+        <v>77.441670000000002</v>
+      </c>
+      <c r="L17" s="35">
+        <v>0.25</v>
       </c>
       <c r="N17" s="35">
         <v>396</v>
@@ -14620,11 +14620,11 @@
       <c r="J18" s="35">
         <v>396</v>
       </c>
-      <c r="K18">
-        <v>68.374223764192124</v>
-      </c>
-      <c r="L18">
-        <v>0.12722553542890438</v>
+      <c r="K18" s="37">
+        <v>76.391670000000005</v>
+      </c>
+      <c r="L18" s="35">
+        <v>0.25</v>
       </c>
       <c r="N18" s="35">
         <v>396</v>
@@ -14667,11 +14667,11 @@
       <c r="J19" s="35">
         <v>396</v>
       </c>
-      <c r="K19">
-        <v>66.6391202803743</v>
-      </c>
-      <c r="L19">
-        <v>0.12399698733577214</v>
+      <c r="K19" s="37">
+        <v>71.533330000000007</v>
+      </c>
+      <c r="L19" s="35">
+        <v>0.25</v>
       </c>
       <c r="N19" s="35">
         <v>396</v>
@@ -14714,11 +14714,11 @@
       <c r="J20" s="35">
         <v>396</v>
       </c>
-      <c r="K20">
-        <v>64.948047776856001</v>
-      </c>
-      <c r="L20">
-        <v>0.12085036872915789</v>
+      <c r="K20" s="37">
+        <v>68.441670000000002</v>
+      </c>
+      <c r="L20" s="35">
+        <v>0.25</v>
       </c>
       <c r="N20" s="35">
         <v>396</v>
@@ -14761,11 +14761,11 @@
       <c r="J21" s="35">
         <v>396</v>
       </c>
-      <c r="K21">
-        <v>63.299888898249371</v>
-      </c>
-      <c r="L21">
-        <v>0.11778360051946238</v>
+      <c r="K21" s="37">
+        <v>65.491669999999999</v>
+      </c>
+      <c r="L21" s="35">
+        <v>0.25</v>
       </c>
       <c r="N21" s="35">
         <v>396</v>
@@ -14808,11 +14808,11 @@
       <c r="J22" s="35">
         <v>396</v>
       </c>
-      <c r="K22">
-        <v>61.693554643817173</v>
-      </c>
-      <c r="L22">
-        <v>0.11479465637725547</v>
+      <c r="K22" s="37">
+        <v>62.683330000000005</v>
+      </c>
+      <c r="L22" s="35">
+        <v>0.25</v>
       </c>
       <c r="N22" s="35">
         <v>396</v>
@@ -14855,11 +14855,11 @@
       <c r="J23" s="35">
         <v>396</v>
       </c>
-      <c r="K23">
-        <v>60.127983647928914</v>
-      </c>
-      <c r="L23">
-        <v>0.11188156139440379</v>
+      <c r="K23" s="37">
+        <v>60</v>
+      </c>
+      <c r="L23" s="35">
+        <v>0.25</v>
       </c>
       <c r="N23" s="35">
         <v>396</v>
@@ -14902,11 +14902,11 @@
       <c r="J24" s="35">
         <v>396</v>
       </c>
-      <c r="K24">
-        <v>58.602141478776574</v>
-      </c>
-      <c r="L24">
-        <v>0.10904239077917448</v>
+      <c r="K24" s="37">
+        <v>57.441669999999995</v>
+      </c>
+      <c r="L24" s="35">
+        <v>0.25</v>
       </c>
       <c r="N24" s="35">
         <v>396</v>
@@ -14949,11 +14949,11 @@
       <c r="J25" s="35">
         <v>396</v>
       </c>
-      <c r="K25">
-        <v>57.115019954886435</v>
-      </c>
-      <c r="L25">
-        <v>0.10627526858445267</v>
+      <c r="K25" s="37">
+        <v>55</v>
+      </c>
+      <c r="L25" s="35">
+        <v>0.25</v>
       </c>
       <c r="N25" s="35">
         <v>396</v>
@@ -14996,11 +14996,11 @@
       <c r="J26" s="35">
         <v>396</v>
       </c>
-      <c r="K26">
-        <v>55.665636478975621</v>
-      </c>
-      <c r="L26">
-        <v>0.10357836646823253</v>
+      <c r="K26" s="37">
+        <v>52.666669999999996</v>
+      </c>
+      <c r="L26" s="35">
+        <v>0.25</v>
       </c>
       <c r="N26" s="35">
         <v>396</v>
@@ -15043,11 +15043,11 @@
       <c r="J27" s="35">
         <v>396</v>
       </c>
-      <c r="K27">
-        <v>54.253033388712979</v>
-      </c>
-      <c r="L27">
-        <v>0.10094990248556265</v>
+      <c r="K27" s="37">
+        <v>50.441669999999995</v>
+      </c>
+      <c r="L27" s="35">
+        <v>0.25</v>
       </c>
       <c r="N27" s="35">
         <v>396</v>
@@ -15090,11 +15090,11 @@
       <c r="J28" s="35">
         <v>396</v>
       </c>
-      <c r="K28">
-        <v>52.876277323955435</v>
-      </c>
-      <c r="L28">
-        <v>9.8388139911147851E-2</v>
+      <c r="K28" s="37">
+        <v>48.316669999999995</v>
+      </c>
+      <c r="L28" s="35">
+        <v>0.25</v>
       </c>
       <c r="N28" s="35">
         <v>396</v>
@@ -15137,11 +15137,11 @@
       <c r="J29" s="35">
         <v>396</v>
       </c>
-      <c r="K29">
-        <v>51.534458610041781</v>
-      </c>
-      <c r="L29">
-        <v>9.5891386091829289E-2</v>
+      <c r="K29" s="37">
+        <v>46.274999999999999</v>
+      </c>
+      <c r="L29" s="35">
+        <v>0.25</v>
       </c>
       <c r="N29" s="35">
         <v>396</v>
@@ -15184,11 +15184,11 @@
       <c r="J30" s="35">
         <v>396</v>
       </c>
-      <c r="K30">
-        <v>50.226690656736288</v>
-      </c>
-      <c r="L30">
-        <v>9.3457991328184623E-2</v>
+      <c r="K30" s="37">
+        <v>44.325000000000003</v>
+      </c>
+      <c r="L30" s="35">
+        <v>0.25</v>
       </c>
       <c r="N30" s="35">
         <v>396</v>
@@ -15231,11 +15231,11 @@
       <c r="J31" s="35">
         <v>396</v>
       </c>
-      <c r="K31">
-        <v>48.95210937242512</v>
-      </c>
-      <c r="L31">
-        <v>9.1086347784509428E-2</v>
+      <c r="K31" s="37">
+        <v>42.458330000000004</v>
+      </c>
+      <c r="L31" s="35">
+        <v>0.25</v>
       </c>
       <c r="N31" s="35">
         <v>396</v>
@@ -15278,11 +15278,11 @@
       <c r="J32" s="35">
         <v>396</v>
       </c>
-      <c r="K32">
-        <v>47.709872593178375</v>
-      </c>
-      <c r="L32">
-        <v>8.8774888426459461E-2</v>
+      <c r="K32" s="37">
+        <v>40.674999999999997</v>
+      </c>
+      <c r="L32" s="35">
+        <v>0.25</v>
       </c>
       <c r="N32" s="35">
         <v>396</v>
